--- a/I TRIMESTRE/1. PROYECTO/Diagrama de gantt.xlsx
+++ b/I TRIMESTRE/1. PROYECTO/Diagrama de gantt.xlsx
@@ -1,14 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sntgo\GRUPO-FIRME\I TRIMESTRE\1. PROYECTO\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA165F76-7210-4C5D-9C85-726BE8941842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Trimestre 1" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Trimestre 2" sheetId="2" r:id="rId5"/>
+    <sheet name="Trimestre 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Trimestre 2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="o58ebRm8na33XWoXi1EBZsyCCC0JoLcRTLJKnqDNOk8="/>
     </ext>
@@ -106,57 +129,60 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="ddd\,\ dd/mm/yyyy"/>
     <numFmt numFmtId="166" formatCode="ddd\,dd/mm/yyyy"/>
     <numFmt numFmtId="167" formatCode="dd"/>
-    <numFmt numFmtId="168" formatCode="D/M/YYYY"/>
+    <numFmt numFmtId="168" formatCode="d/m/yyyy"/>
   </numFmts>
   <fonts count="9">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
     </font>
-    <font/>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
-      <sz val="9.0"/>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
       <b/>
-      <sz val="9.0"/>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="10"/>
       <name val="Aptos Narrow"/>
     </font>
@@ -166,7 +192,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -200,29 +226,42 @@
     </fill>
   </fills>
   <borders count="17">
-    <border/>
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -230,20 +269,25 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-    </border>
-    <border>
       <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -256,6 +300,7 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -270,19 +315,23 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -292,6 +341,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -300,6 +350,7 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -308,6 +359,7 @@
       </right>
       <top/>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -318,6 +370,7 @@
       </right>
       <top/>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -330,139 +383,158 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="1"/>
       </top>
       <bottom style="thin">
         <color theme="1"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="1"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="37">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="3" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="6" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="3" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="4" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="8" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf borderId="9" fillId="5" fontId="1" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="10" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="11" fillId="3" fontId="6" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="6" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="12" fillId="3" fontId="6" numFmtId="167" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="13" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="1" fillId="6" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="14" fillId="6" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="15" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="15" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="15" fillId="0" fontId="1" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="15" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="15" fillId="0" fontId="7" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="16" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="16" fillId="0" fontId="1" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="16" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="168" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="168" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
     <dxf>
-      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9F2D0"/>
+          <bgColor rgb="FFD9F2D0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF8ED873"/>
           <bgColor rgb="FF8ED873"/>
         </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFD9F2D0"/>
           <bgColor rgb="FFD9F2D0"/>
         </patternFill>
       </fill>
-      <border/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF8ED873"/>
+          <bgColor rgb="FF8ED873"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -652,1295 +724,1297 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FF215E99"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:AN1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="15.75"/>
-    <col customWidth="1" min="3" max="5" width="11.75"/>
-    <col customWidth="1" min="6" max="39" width="3.75"/>
-    <col customWidth="1" min="40" max="40" width="13.75"/>
+    <col min="1" max="2" width="15.77734375" customWidth="1"/>
+    <col min="3" max="5" width="11.77734375" customWidth="1"/>
+    <col min="6" max="39" width="3.77734375" customWidth="1"/>
+    <col min="40" max="40" width="13.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1"/>
-    <row r="2" ht="14.25" customHeight="1"/>
-    <row r="3" ht="14.25" customHeight="1"/>
-    <row r="4" ht="19.5" customHeight="1">
+    <row r="1" spans="1:40" ht="14.25" customHeight="1"/>
+    <row r="2" spans="1:40" ht="14.25" customHeight="1"/>
+    <row r="3" spans="1:40" ht="14.25" customHeight="1"/>
+    <row r="4" spans="1:40" ht="19.5" customHeight="1">
       <c r="D4" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2">
         <f>D5+D4</f>
         <v>45930</v>
       </c>
       <c r="F4" s="3"/>
-      <c r="G4" s="4">
+      <c r="G4" s="30">
         <f>G5</f>
         <v>45930</v>
       </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="4">
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="32"/>
+      <c r="L4" s="30">
         <f>L5</f>
         <v>45935</v>
       </c>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="4">
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
+      <c r="O4" s="31"/>
+      <c r="P4" s="31"/>
+      <c r="Q4" s="31"/>
+      <c r="R4" s="32"/>
+      <c r="S4" s="30">
         <f>S5</f>
         <v>45942</v>
       </c>
-      <c r="T4" s="5"/>
-      <c r="U4" s="5"/>
-      <c r="V4" s="5"/>
-      <c r="W4" s="5"/>
-      <c r="X4" s="5"/>
-      <c r="Y4" s="6"/>
-      <c r="Z4" s="4">
+      <c r="T4" s="31"/>
+      <c r="U4" s="31"/>
+      <c r="V4" s="31"/>
+      <c r="W4" s="31"/>
+      <c r="X4" s="31"/>
+      <c r="Y4" s="32"/>
+      <c r="Z4" s="30">
         <f>Z5</f>
         <v>45949</v>
       </c>
-      <c r="AA4" s="5"/>
-      <c r="AB4" s="5"/>
-      <c r="AC4" s="5"/>
-      <c r="AD4" s="5"/>
-      <c r="AE4" s="5"/>
-      <c r="AF4" s="6"/>
-      <c r="AG4" s="7">
+      <c r="AA4" s="31"/>
+      <c r="AB4" s="31"/>
+      <c r="AC4" s="31"/>
+      <c r="AD4" s="31"/>
+      <c r="AE4" s="31"/>
+      <c r="AF4" s="32"/>
+      <c r="AG4" s="33">
         <f>AG5</f>
         <v>45956</v>
       </c>
-      <c r="AH4" s="5"/>
-      <c r="AI4" s="5"/>
-      <c r="AJ4" s="5"/>
-      <c r="AK4" s="5"/>
-      <c r="AL4" s="5"/>
-      <c r="AM4" s="8"/>
-      <c r="AN4" s="9" t="s">
+      <c r="AH4" s="31"/>
+      <c r="AI4" s="31"/>
+      <c r="AJ4" s="31"/>
+      <c r="AK4" s="31"/>
+      <c r="AL4" s="31"/>
+      <c r="AM4" s="34"/>
+      <c r="AN4" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" ht="14.25" customHeight="1">
-      <c r="B5" s="10"/>
-      <c r="C5" s="11" t="s">
+    <row r="5" spans="1:40" ht="14.25" customHeight="1">
+      <c r="B5" s="5"/>
+      <c r="C5" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="35">
         <f>DATE(2025,10,1)+$D$4-1</f>
         <v>45930</v>
       </c>
-      <c r="E5" s="13"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="15">
+      <c r="E5" s="36"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="8">
         <f>D5</f>
         <v>45930</v>
       </c>
-      <c r="H5" s="16">
-        <f t="shared" ref="H5:AM5" si="1">G5+1</f>
+      <c r="H5" s="9">
+        <f t="shared" ref="H5:AM5" si="0">G5+1</f>
         <v>45931</v>
       </c>
-      <c r="I5" s="16">
-        <f t="shared" si="1"/>
+      <c r="I5" s="9">
+        <f t="shared" si="0"/>
         <v>45932</v>
       </c>
-      <c r="J5" s="16">
-        <f t="shared" si="1"/>
+      <c r="J5" s="9">
+        <f t="shared" si="0"/>
         <v>45933</v>
       </c>
-      <c r="K5" s="17">
-        <f t="shared" si="1"/>
+      <c r="K5" s="10">
+        <f t="shared" si="0"/>
         <v>45934</v>
       </c>
-      <c r="L5" s="15">
-        <f t="shared" si="1"/>
+      <c r="L5" s="8">
+        <f t="shared" si="0"/>
         <v>45935</v>
       </c>
-      <c r="M5" s="16">
-        <f t="shared" si="1"/>
+      <c r="M5" s="9">
+        <f t="shared" si="0"/>
         <v>45936</v>
       </c>
-      <c r="N5" s="16">
-        <f t="shared" si="1"/>
+      <c r="N5" s="9">
+        <f t="shared" si="0"/>
         <v>45937</v>
       </c>
-      <c r="O5" s="16">
-        <f t="shared" si="1"/>
+      <c r="O5" s="9">
+        <f t="shared" si="0"/>
         <v>45938</v>
       </c>
-      <c r="P5" s="16">
-        <f t="shared" si="1"/>
+      <c r="P5" s="9">
+        <f t="shared" si="0"/>
         <v>45939</v>
       </c>
-      <c r="Q5" s="16">
-        <f t="shared" si="1"/>
+      <c r="Q5" s="9">
+        <f t="shared" si="0"/>
         <v>45940</v>
       </c>
-      <c r="R5" s="17">
-        <f t="shared" si="1"/>
+      <c r="R5" s="10">
+        <f t="shared" si="0"/>
         <v>45941</v>
       </c>
-      <c r="S5" s="15">
-        <f t="shared" si="1"/>
+      <c r="S5" s="8">
+        <f t="shared" si="0"/>
         <v>45942</v>
       </c>
-      <c r="T5" s="16">
-        <f t="shared" si="1"/>
+      <c r="T5" s="9">
+        <f t="shared" si="0"/>
         <v>45943</v>
       </c>
-      <c r="U5" s="16">
-        <f t="shared" si="1"/>
+      <c r="U5" s="9">
+        <f t="shared" si="0"/>
         <v>45944</v>
       </c>
-      <c r="V5" s="16">
-        <f t="shared" si="1"/>
+      <c r="V5" s="9">
+        <f t="shared" si="0"/>
         <v>45945</v>
       </c>
-      <c r="W5" s="16">
-        <f t="shared" si="1"/>
+      <c r="W5" s="9">
+        <f t="shared" si="0"/>
         <v>45946</v>
       </c>
-      <c r="X5" s="16">
-        <f t="shared" si="1"/>
+      <c r="X5" s="9">
+        <f t="shared" si="0"/>
         <v>45947</v>
       </c>
-      <c r="Y5" s="17">
-        <f t="shared" si="1"/>
+      <c r="Y5" s="10">
+        <f t="shared" si="0"/>
         <v>45948</v>
       </c>
-      <c r="Z5" s="15">
-        <f t="shared" si="1"/>
+      <c r="Z5" s="8">
+        <f t="shared" si="0"/>
         <v>45949</v>
       </c>
-      <c r="AA5" s="16">
-        <f t="shared" si="1"/>
+      <c r="AA5" s="9">
+        <f t="shared" si="0"/>
         <v>45950</v>
       </c>
-      <c r="AB5" s="16">
-        <f t="shared" si="1"/>
+      <c r="AB5" s="9">
+        <f t="shared" si="0"/>
         <v>45951</v>
       </c>
-      <c r="AC5" s="16">
-        <f t="shared" si="1"/>
+      <c r="AC5" s="9">
+        <f t="shared" si="0"/>
         <v>45952</v>
       </c>
-      <c r="AD5" s="16">
-        <f t="shared" si="1"/>
+      <c r="AD5" s="9">
+        <f t="shared" si="0"/>
         <v>45953</v>
       </c>
-      <c r="AE5" s="16">
-        <f t="shared" si="1"/>
+      <c r="AE5" s="9">
+        <f t="shared" si="0"/>
         <v>45954</v>
       </c>
-      <c r="AF5" s="17">
-        <f t="shared" si="1"/>
+      <c r="AF5" s="10">
+        <f t="shared" si="0"/>
         <v>45955</v>
       </c>
-      <c r="AG5" s="16">
-        <f t="shared" si="1"/>
+      <c r="AG5" s="9">
+        <f t="shared" si="0"/>
         <v>45956</v>
       </c>
-      <c r="AH5" s="16">
-        <f t="shared" si="1"/>
+      <c r="AH5" s="9">
+        <f t="shared" si="0"/>
         <v>45957</v>
       </c>
-      <c r="AI5" s="16">
-        <f t="shared" si="1"/>
+      <c r="AI5" s="9">
+        <f t="shared" si="0"/>
         <v>45958</v>
       </c>
-      <c r="AJ5" s="16">
-        <f t="shared" si="1"/>
+      <c r="AJ5" s="9">
+        <f t="shared" si="0"/>
         <v>45959</v>
       </c>
-      <c r="AK5" s="16">
-        <f t="shared" si="1"/>
+      <c r="AK5" s="9">
+        <f t="shared" si="0"/>
         <v>45960</v>
       </c>
-      <c r="AL5" s="16">
-        <f t="shared" si="1"/>
+      <c r="AL5" s="9">
+        <f t="shared" si="0"/>
         <v>45961</v>
       </c>
-      <c r="AM5" s="16">
-        <f t="shared" si="1"/>
+      <c r="AM5" s="9">
+        <f t="shared" si="0"/>
         <v>45962</v>
       </c>
-      <c r="AN5" s="18" t="s">
+      <c r="AN5" s="11" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" ht="19.5" customHeight="1">
-      <c r="A6" s="19" t="s">
+    <row r="6" spans="1:40" ht="19.5" customHeight="1">
+      <c r="A6" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="20"/>
-      <c r="G6" s="21" t="str">
-        <f t="shared" ref="G6:AM6" si="2">UPPER(LEFT(TEXT(G5,"ddd"),1))</f>
+      <c r="F6" s="13"/>
+      <c r="G6" s="14" t="str">
+        <f t="shared" ref="G6:AM6" si="1">UPPER(LEFT(TEXT(G5,"ddd"),1))</f>
         <v>M</v>
       </c>
-      <c r="H6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="H6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>M</v>
       </c>
-      <c r="I6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="I6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>J</v>
       </c>
-      <c r="J6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="J6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>V</v>
       </c>
-      <c r="K6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="K6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>S</v>
       </c>
-      <c r="L6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="L6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>D</v>
       </c>
-      <c r="M6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="M6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="N6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="N6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>M</v>
       </c>
-      <c r="O6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="O6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>M</v>
       </c>
-      <c r="P6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="P6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>J</v>
       </c>
-      <c r="Q6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="Q6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>V</v>
       </c>
-      <c r="R6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="R6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>S</v>
       </c>
-      <c r="S6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="S6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>D</v>
       </c>
-      <c r="T6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="T6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="U6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="U6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>M</v>
       </c>
-      <c r="V6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="V6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>M</v>
       </c>
-      <c r="W6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="W6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>J</v>
       </c>
-      <c r="X6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="X6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>V</v>
       </c>
-      <c r="Y6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="Y6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>S</v>
       </c>
-      <c r="Z6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="Z6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>D</v>
       </c>
-      <c r="AA6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="AA6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="AB6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="AB6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>M</v>
       </c>
-      <c r="AC6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="AC6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>M</v>
       </c>
-      <c r="AD6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="AD6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>J</v>
       </c>
-      <c r="AE6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="AE6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>V</v>
       </c>
-      <c r="AF6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="AF6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>S</v>
       </c>
-      <c r="AG6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="AG6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>D</v>
       </c>
-      <c r="AH6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="AH6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="AI6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="AI6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>M</v>
       </c>
-      <c r="AJ6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="AJ6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>M</v>
       </c>
-      <c r="AK6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="AK6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>J</v>
       </c>
-      <c r="AL6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="AL6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>V</v>
       </c>
-      <c r="AM6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="AM6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>S</v>
       </c>
-      <c r="AN6" s="22"/>
+      <c r="AN6" s="15"/>
     </row>
-    <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="23" t="s">
+    <row r="7" spans="1:40" ht="14.25" customHeight="1">
+      <c r="A7" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="24"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="24"/>
-      <c r="N7" s="24"/>
-      <c r="O7" s="24"/>
-      <c r="P7" s="24"/>
-      <c r="Q7" s="24"/>
-      <c r="R7" s="24"/>
-      <c r="S7" s="24"/>
-      <c r="T7" s="24"/>
-      <c r="U7" s="24"/>
-      <c r="V7" s="24"/>
-      <c r="W7" s="24"/>
-      <c r="X7" s="24"/>
-      <c r="Y7" s="24"/>
-      <c r="Z7" s="24"/>
-      <c r="AA7" s="24"/>
-      <c r="AB7" s="24"/>
-      <c r="AC7" s="24"/>
-      <c r="AD7" s="24"/>
-      <c r="AE7" s="24"/>
-      <c r="AF7" s="24"/>
-      <c r="AG7" s="24"/>
-      <c r="AH7" s="24"/>
-      <c r="AI7" s="24"/>
-      <c r="AJ7" s="24"/>
-      <c r="AK7" s="24"/>
-      <c r="AL7" s="24"/>
-      <c r="AM7" s="24"/>
-      <c r="AN7" s="27"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="17"/>
+      <c r="Q7" s="17"/>
+      <c r="R7" s="17"/>
+      <c r="S7" s="17"/>
+      <c r="T7" s="17"/>
+      <c r="U7" s="17"/>
+      <c r="V7" s="17"/>
+      <c r="W7" s="17"/>
+      <c r="X7" s="17"/>
+      <c r="Y7" s="17"/>
+      <c r="Z7" s="17"/>
+      <c r="AA7" s="17"/>
+      <c r="AB7" s="17"/>
+      <c r="AC7" s="17"/>
+      <c r="AD7" s="17"/>
+      <c r="AE7" s="17"/>
+      <c r="AF7" s="17"/>
+      <c r="AG7" s="17"/>
+      <c r="AH7" s="17"/>
+      <c r="AI7" s="17"/>
+      <c r="AJ7" s="17"/>
+      <c r="AK7" s="17"/>
+      <c r="AL7" s="17"/>
+      <c r="AM7" s="17"/>
+      <c r="AN7" s="20"/>
     </row>
-    <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="24" t="s">
+    <row r="8" spans="1:40" ht="14.25" customHeight="1">
+      <c r="A8" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="28">
-        <v>1.0</v>
-      </c>
-      <c r="D8" s="26">
-        <v>45930.0</v>
-      </c>
-      <c r="E8" s="26">
-        <v>45943.0</v>
-      </c>
-      <c r="F8" s="24"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="24"/>
-      <c r="I8" s="24"/>
-      <c r="J8" s="24"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="24"/>
-      <c r="M8" s="24"/>
-      <c r="N8" s="24"/>
-      <c r="O8" s="24"/>
-      <c r="P8" s="24"/>
-      <c r="Q8" s="24"/>
-      <c r="R8" s="24"/>
-      <c r="S8" s="24"/>
-      <c r="T8" s="24"/>
-      <c r="U8" s="24"/>
-      <c r="V8" s="24"/>
-      <c r="W8" s="24"/>
-      <c r="X8" s="24"/>
-      <c r="Y8" s="24"/>
-      <c r="Z8" s="24"/>
-      <c r="AA8" s="24"/>
-      <c r="AB8" s="24"/>
-      <c r="AC8" s="24"/>
-      <c r="AD8" s="24"/>
-      <c r="AE8" s="24"/>
-      <c r="AF8" s="24"/>
-      <c r="AG8" s="24"/>
-      <c r="AH8" s="24"/>
-      <c r="AI8" s="24"/>
-      <c r="AJ8" s="24"/>
-      <c r="AK8" s="24"/>
-      <c r="AL8" s="24"/>
-      <c r="AM8" s="24"/>
-      <c r="AN8" s="29" t="str">
+      <c r="C8" s="21">
+        <v>1</v>
+      </c>
+      <c r="D8" s="19">
+        <v>45930</v>
+      </c>
+      <c r="E8" s="19">
+        <v>45943</v>
+      </c>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="17"/>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="17"/>
+      <c r="R8" s="17"/>
+      <c r="S8" s="17"/>
+      <c r="T8" s="17"/>
+      <c r="U8" s="17"/>
+      <c r="V8" s="17"/>
+      <c r="W8" s="17"/>
+      <c r="X8" s="17"/>
+      <c r="Y8" s="17"/>
+      <c r="Z8" s="17"/>
+      <c r="AA8" s="17"/>
+      <c r="AB8" s="17"/>
+      <c r="AC8" s="17"/>
+      <c r="AD8" s="17"/>
+      <c r="AE8" s="17"/>
+      <c r="AF8" s="17"/>
+      <c r="AG8" s="17"/>
+      <c r="AH8" s="17"/>
+      <c r="AI8" s="17"/>
+      <c r="AJ8" s="17"/>
+      <c r="AK8" s="17"/>
+      <c r="AL8" s="17"/>
+      <c r="AM8" s="17"/>
+      <c r="AN8" s="22" t="str">
         <f>HYPERLINK("https://docs.google.com/document/d/1SfObwPSfjVAwlpyIXOPeG8gmHfwh27uKPV4VENBtBxM/edit?usp=sharing", "Abrir")</f>
         <v>Abrir</v>
       </c>
     </row>
-    <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="24" t="s">
+    <row r="9" spans="1:40" ht="14.25" customHeight="1">
+      <c r="A9" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="25">
-        <v>1.0</v>
-      </c>
-      <c r="D9" s="26">
-        <v>45930.0</v>
-      </c>
-      <c r="E9" s="26">
-        <v>45942.0</v>
-      </c>
-      <c r="F9" s="24"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="24"/>
-      <c r="I9" s="24"/>
-      <c r="J9" s="24"/>
-      <c r="K9" s="24"/>
-      <c r="L9" s="24"/>
-      <c r="M9" s="24"/>
-      <c r="N9" s="24"/>
-      <c r="O9" s="24"/>
-      <c r="P9" s="24"/>
-      <c r="Q9" s="24"/>
-      <c r="R9" s="24"/>
-      <c r="S9" s="24"/>
-      <c r="T9" s="24"/>
-      <c r="U9" s="24"/>
-      <c r="V9" s="24"/>
-      <c r="W9" s="24"/>
-      <c r="X9" s="24"/>
-      <c r="Y9" s="24"/>
-      <c r="Z9" s="24"/>
-      <c r="AA9" s="24"/>
-      <c r="AB9" s="24"/>
-      <c r="AC9" s="24"/>
-      <c r="AD9" s="24"/>
-      <c r="AE9" s="24"/>
-      <c r="AF9" s="24"/>
-      <c r="AG9" s="24"/>
-      <c r="AH9" s="24"/>
-      <c r="AI9" s="24"/>
-      <c r="AJ9" s="24"/>
-      <c r="AK9" s="24"/>
-      <c r="AL9" s="24"/>
-      <c r="AM9" s="24"/>
-      <c r="AN9" s="29" t="str">
-        <f t="shared" ref="AN9:AN10" si="3">HYPERLINK("https://docs.google.com/document/d/1trIHa_v8WPWOT3NTyg-kcsC2C-ug-amAs7e9WZ1nZaY/edit?usp=drive_link","Abrir")</f>
+      <c r="C9" s="18">
+        <v>1</v>
+      </c>
+      <c r="D9" s="19">
+        <v>45930</v>
+      </c>
+      <c r="E9" s="19">
+        <v>45942</v>
+      </c>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17"/>
+      <c r="R9" s="17"/>
+      <c r="S9" s="17"/>
+      <c r="T9" s="17"/>
+      <c r="U9" s="17"/>
+      <c r="V9" s="17"/>
+      <c r="W9" s="17"/>
+      <c r="X9" s="17"/>
+      <c r="Y9" s="17"/>
+      <c r="Z9" s="17"/>
+      <c r="AA9" s="17"/>
+      <c r="AB9" s="17"/>
+      <c r="AC9" s="17"/>
+      <c r="AD9" s="17"/>
+      <c r="AE9" s="17"/>
+      <c r="AF9" s="17"/>
+      <c r="AG9" s="17"/>
+      <c r="AH9" s="17"/>
+      <c r="AI9" s="17"/>
+      <c r="AJ9" s="17"/>
+      <c r="AK9" s="17"/>
+      <c r="AL9" s="17"/>
+      <c r="AM9" s="17"/>
+      <c r="AN9" s="22" t="str">
+        <f t="shared" ref="AN9:AN10" si="2">HYPERLINK("https://docs.google.com/document/d/1trIHa_v8WPWOT3NTyg-kcsC2C-ug-amAs7e9WZ1nZaY/edit?usp=drive_link","Abrir")</f>
         <v>Abrir</v>
       </c>
     </row>
-    <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="24" t="s">
+    <row r="10" spans="1:40" ht="14.25" customHeight="1">
+      <c r="A10" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="25">
-        <v>1.0</v>
-      </c>
-      <c r="D10" s="26">
-        <v>45930.0</v>
-      </c>
-      <c r="E10" s="26">
-        <v>45942.0</v>
-      </c>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="24"/>
-      <c r="M10" s="24"/>
-      <c r="N10" s="24"/>
-      <c r="O10" s="24"/>
-      <c r="P10" s="24"/>
-      <c r="Q10" s="24"/>
-      <c r="R10" s="24"/>
-      <c r="S10" s="24"/>
-      <c r="T10" s="24"/>
-      <c r="U10" s="24"/>
-      <c r="V10" s="24"/>
-      <c r="W10" s="24"/>
-      <c r="X10" s="24"/>
-      <c r="Y10" s="24"/>
-      <c r="Z10" s="24"/>
-      <c r="AA10" s="24"/>
-      <c r="AB10" s="24"/>
-      <c r="AC10" s="24"/>
-      <c r="AD10" s="24"/>
-      <c r="AE10" s="24"/>
-      <c r="AF10" s="24"/>
-      <c r="AG10" s="24"/>
-      <c r="AH10" s="24"/>
-      <c r="AI10" s="24"/>
-      <c r="AJ10" s="24"/>
-      <c r="AK10" s="24"/>
-      <c r="AL10" s="24"/>
-      <c r="AM10" s="24"/>
-      <c r="AN10" s="29" t="str">
+      <c r="C10" s="18">
+        <v>1</v>
+      </c>
+      <c r="D10" s="19">
+        <v>45930</v>
+      </c>
+      <c r="E10" s="19">
+        <v>45942</v>
+      </c>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="17"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="17"/>
+      <c r="S10" s="17"/>
+      <c r="T10" s="17"/>
+      <c r="U10" s="17"/>
+      <c r="V10" s="17"/>
+      <c r="W10" s="17"/>
+      <c r="X10" s="17"/>
+      <c r="Y10" s="17"/>
+      <c r="Z10" s="17"/>
+      <c r="AA10" s="17"/>
+      <c r="AB10" s="17"/>
+      <c r="AC10" s="17"/>
+      <c r="AD10" s="17"/>
+      <c r="AE10" s="17"/>
+      <c r="AF10" s="17"/>
+      <c r="AG10" s="17"/>
+      <c r="AH10" s="17"/>
+      <c r="AI10" s="17"/>
+      <c r="AJ10" s="17"/>
+      <c r="AK10" s="17"/>
+      <c r="AL10" s="17"/>
+      <c r="AM10" s="17"/>
+      <c r="AN10" s="22" t="str">
+        <f t="shared" si="2"/>
+        <v>Abrir</v>
+      </c>
+    </row>
+    <row r="11" spans="1:40" ht="14.25" customHeight="1">
+      <c r="A11" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="18">
+        <v>1</v>
+      </c>
+      <c r="D11" s="19">
+        <v>45930</v>
+      </c>
+      <c r="E11" s="19">
+        <v>45943</v>
+      </c>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="17"/>
+      <c r="S11" s="17"/>
+      <c r="T11" s="17"/>
+      <c r="U11" s="17"/>
+      <c r="V11" s="17"/>
+      <c r="W11" s="17"/>
+      <c r="X11" s="17"/>
+      <c r="Y11" s="17"/>
+      <c r="Z11" s="17"/>
+      <c r="AA11" s="17"/>
+      <c r="AB11" s="17"/>
+      <c r="AC11" s="17"/>
+      <c r="AD11" s="17"/>
+      <c r="AE11" s="17"/>
+      <c r="AF11" s="17"/>
+      <c r="AG11" s="17"/>
+      <c r="AH11" s="17"/>
+      <c r="AI11" s="17"/>
+      <c r="AJ11" s="17"/>
+      <c r="AK11" s="17"/>
+      <c r="AL11" s="17"/>
+      <c r="AM11" s="17"/>
+      <c r="AN11" s="22" t="str">
+        <f t="shared" ref="AN11:AN12" si="3">HYPERLINK("https://docs.google.com/document/d/1SfObwPSfjVAwlpyIXOPeG8gmHfwh27uKPV4VENBtBxM/edit?usp=drive_link","Abrir")</f>
+        <v>Abrir</v>
+      </c>
+    </row>
+    <row r="12" spans="1:40" ht="14.25" customHeight="1">
+      <c r="A12" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="18">
+        <v>1</v>
+      </c>
+      <c r="D12" s="19">
+        <v>45930</v>
+      </c>
+      <c r="E12" s="19">
+        <v>45947</v>
+      </c>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17"/>
+      <c r="R12" s="17"/>
+      <c r="S12" s="17"/>
+      <c r="T12" s="17"/>
+      <c r="U12" s="17"/>
+      <c r="V12" s="17"/>
+      <c r="W12" s="17"/>
+      <c r="X12" s="17"/>
+      <c r="Y12" s="17"/>
+      <c r="Z12" s="17"/>
+      <c r="AA12" s="17"/>
+      <c r="AB12" s="17"/>
+      <c r="AC12" s="17"/>
+      <c r="AD12" s="17"/>
+      <c r="AE12" s="17"/>
+      <c r="AF12" s="17"/>
+      <c r="AG12" s="17"/>
+      <c r="AH12" s="17"/>
+      <c r="AI12" s="17"/>
+      <c r="AJ12" s="17"/>
+      <c r="AK12" s="17"/>
+      <c r="AL12" s="17"/>
+      <c r="AM12" s="17"/>
+      <c r="AN12" s="22" t="str">
         <f t="shared" si="3"/>
         <v>Abrir</v>
       </c>
     </row>
-    <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="25">
-        <v>1.0</v>
-      </c>
-      <c r="D11" s="26">
-        <v>45930.0</v>
-      </c>
-      <c r="E11" s="26">
-        <v>45943.0</v>
-      </c>
-      <c r="F11" s="24"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="24"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="24"/>
-      <c r="K11" s="24"/>
-      <c r="L11" s="24"/>
-      <c r="M11" s="24"/>
-      <c r="N11" s="24"/>
-      <c r="O11" s="24"/>
-      <c r="P11" s="24"/>
-      <c r="Q11" s="24"/>
-      <c r="R11" s="24"/>
-      <c r="S11" s="24"/>
-      <c r="T11" s="24"/>
-      <c r="U11" s="24"/>
-      <c r="V11" s="24"/>
-      <c r="W11" s="24"/>
-      <c r="X11" s="24"/>
-      <c r="Y11" s="24"/>
-      <c r="Z11" s="24"/>
-      <c r="AA11" s="24"/>
-      <c r="AB11" s="24"/>
-      <c r="AC11" s="24"/>
-      <c r="AD11" s="24"/>
-      <c r="AE11" s="24"/>
-      <c r="AF11" s="24"/>
-      <c r="AG11" s="24"/>
-      <c r="AH11" s="24"/>
-      <c r="AI11" s="24"/>
-      <c r="AJ11" s="24"/>
-      <c r="AK11" s="24"/>
-      <c r="AL11" s="24"/>
-      <c r="AM11" s="24"/>
-      <c r="AN11" s="29" t="str">
-        <f t="shared" ref="AN11:AN12" si="4">HYPERLINK("https://docs.google.com/document/d/1SfObwPSfjVAwlpyIXOPeG8gmHfwh27uKPV4VENBtBxM/edit?usp=drive_link","Abrir")</f>
-        <v>Abrir</v>
-      </c>
+    <row r="13" spans="1:40" ht="14.25" customHeight="1">
+      <c r="A13" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="18">
+        <v>1</v>
+      </c>
+      <c r="D13" s="19">
+        <v>45930</v>
+      </c>
+      <c r="E13" s="19">
+        <v>45935</v>
+      </c>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17"/>
+      <c r="R13" s="17"/>
+      <c r="S13" s="17"/>
+      <c r="T13" s="17"/>
+      <c r="U13" s="17"/>
+      <c r="V13" s="17"/>
+      <c r="W13" s="17"/>
+      <c r="X13" s="17"/>
+      <c r="Y13" s="17"/>
+      <c r="Z13" s="17"/>
+      <c r="AA13" s="17"/>
+      <c r="AB13" s="17"/>
+      <c r="AC13" s="17"/>
+      <c r="AD13" s="17"/>
+      <c r="AE13" s="17"/>
+      <c r="AF13" s="17"/>
+      <c r="AG13" s="17"/>
+      <c r="AH13" s="17"/>
+      <c r="AI13" s="17"/>
+      <c r="AJ13" s="17"/>
+      <c r="AK13" s="17"/>
+      <c r="AL13" s="17"/>
+      <c r="AM13" s="17"/>
+      <c r="AN13" s="20"/>
     </row>
-    <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="25">
-        <v>1.0</v>
-      </c>
-      <c r="D12" s="26">
-        <v>45930.0</v>
-      </c>
-      <c r="E12" s="26">
-        <v>45947.0</v>
-      </c>
-      <c r="F12" s="24"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="24"/>
-      <c r="I12" s="24"/>
-      <c r="J12" s="24"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="24"/>
-      <c r="M12" s="24"/>
-      <c r="N12" s="24"/>
-      <c r="O12" s="24"/>
-      <c r="P12" s="24"/>
-      <c r="Q12" s="24"/>
-      <c r="R12" s="24"/>
-      <c r="S12" s="24"/>
-      <c r="T12" s="24"/>
-      <c r="U12" s="24"/>
-      <c r="V12" s="24"/>
-      <c r="W12" s="24"/>
-      <c r="X12" s="24"/>
-      <c r="Y12" s="24"/>
-      <c r="Z12" s="24"/>
-      <c r="AA12" s="24"/>
-      <c r="AB12" s="24"/>
-      <c r="AC12" s="24"/>
-      <c r="AD12" s="24"/>
-      <c r="AE12" s="24"/>
-      <c r="AF12" s="24"/>
-      <c r="AG12" s="24"/>
-      <c r="AH12" s="24"/>
-      <c r="AI12" s="24"/>
-      <c r="AJ12" s="24"/>
-      <c r="AK12" s="24"/>
-      <c r="AL12" s="24"/>
-      <c r="AM12" s="24"/>
-      <c r="AN12" s="29" t="str">
-        <f t="shared" si="4"/>
-        <v>Abrir</v>
-      </c>
+    <row r="14" spans="1:40" ht="14.25" customHeight="1">
+      <c r="A14" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="18">
+        <v>1</v>
+      </c>
+      <c r="D14" s="19">
+        <v>45930</v>
+      </c>
+      <c r="E14" s="19">
+        <v>45947</v>
+      </c>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="17"/>
+      <c r="R14" s="17"/>
+      <c r="S14" s="17"/>
+      <c r="T14" s="17"/>
+      <c r="U14" s="17"/>
+      <c r="V14" s="17"/>
+      <c r="W14" s="17"/>
+      <c r="X14" s="17"/>
+      <c r="Y14" s="17"/>
+      <c r="Z14" s="17"/>
+      <c r="AA14" s="17"/>
+      <c r="AB14" s="17"/>
+      <c r="AC14" s="17"/>
+      <c r="AD14" s="17"/>
+      <c r="AE14" s="17"/>
+      <c r="AF14" s="17"/>
+      <c r="AG14" s="17"/>
+      <c r="AH14" s="17"/>
+      <c r="AI14" s="17"/>
+      <c r="AJ14" s="17"/>
+      <c r="AK14" s="17"/>
+      <c r="AL14" s="17"/>
+      <c r="AM14" s="17"/>
+      <c r="AN14" s="20"/>
     </row>
-    <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="25">
-        <v>1.0</v>
-      </c>
-      <c r="D13" s="26">
-        <v>45930.0</v>
-      </c>
-      <c r="E13" s="26">
-        <v>45935.0</v>
-      </c>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="24"/>
-      <c r="I13" s="24"/>
-      <c r="J13" s="24"/>
-      <c r="K13" s="24"/>
-      <c r="L13" s="24"/>
-      <c r="M13" s="24"/>
-      <c r="N13" s="24"/>
-      <c r="O13" s="24"/>
-      <c r="P13" s="24"/>
-      <c r="Q13" s="24"/>
-      <c r="R13" s="24"/>
-      <c r="S13" s="24"/>
-      <c r="T13" s="24"/>
-      <c r="U13" s="24"/>
-      <c r="V13" s="24"/>
-      <c r="W13" s="24"/>
-      <c r="X13" s="24"/>
-      <c r="Y13" s="24"/>
-      <c r="Z13" s="24"/>
-      <c r="AA13" s="24"/>
-      <c r="AB13" s="24"/>
-      <c r="AC13" s="24"/>
-      <c r="AD13" s="24"/>
-      <c r="AE13" s="24"/>
-      <c r="AF13" s="24"/>
-      <c r="AG13" s="24"/>
-      <c r="AH13" s="24"/>
-      <c r="AI13" s="24"/>
-      <c r="AJ13" s="24"/>
-      <c r="AK13" s="24"/>
-      <c r="AL13" s="24"/>
-      <c r="AM13" s="24"/>
-      <c r="AN13" s="27"/>
-    </row>
-    <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="25">
-        <v>1.0</v>
-      </c>
-      <c r="D14" s="26">
-        <v>45930.0</v>
-      </c>
-      <c r="E14" s="26">
-        <v>45947.0</v>
-      </c>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="24"/>
-      <c r="K14" s="24"/>
-      <c r="L14" s="24"/>
-      <c r="M14" s="24"/>
-      <c r="N14" s="24"/>
-      <c r="O14" s="24"/>
-      <c r="P14" s="24"/>
-      <c r="Q14" s="24"/>
-      <c r="R14" s="24"/>
-      <c r="S14" s="24"/>
-      <c r="T14" s="24"/>
-      <c r="U14" s="24"/>
-      <c r="V14" s="24"/>
-      <c r="W14" s="24"/>
-      <c r="X14" s="24"/>
-      <c r="Y14" s="24"/>
-      <c r="Z14" s="24"/>
-      <c r="AA14" s="24"/>
-      <c r="AB14" s="24"/>
-      <c r="AC14" s="24"/>
-      <c r="AD14" s="24"/>
-      <c r="AE14" s="24"/>
-      <c r="AF14" s="24"/>
-      <c r="AG14" s="24"/>
-      <c r="AH14" s="24"/>
-      <c r="AI14" s="24"/>
-      <c r="AJ14" s="24"/>
-      <c r="AK14" s="24"/>
-      <c r="AL14" s="24"/>
-      <c r="AM14" s="24"/>
-      <c r="AN14" s="27"/>
-    </row>
-    <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="24" t="s">
+    <row r="15" spans="1:40" ht="14.25" customHeight="1">
+      <c r="A15" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="25">
-        <v>1.0</v>
-      </c>
-      <c r="D15" s="26">
-        <v>45930.0</v>
-      </c>
-      <c r="E15" s="26">
-        <v>45946.0</v>
-      </c>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="24"/>
-      <c r="K15" s="24"/>
-      <c r="L15" s="24"/>
-      <c r="M15" s="24"/>
-      <c r="N15" s="24"/>
-      <c r="O15" s="24"/>
-      <c r="P15" s="24"/>
-      <c r="Q15" s="24"/>
-      <c r="R15" s="24"/>
-      <c r="S15" s="24"/>
-      <c r="T15" s="24"/>
-      <c r="U15" s="24"/>
-      <c r="V15" s="24"/>
-      <c r="W15" s="24"/>
-      <c r="X15" s="24"/>
-      <c r="Y15" s="24"/>
-      <c r="Z15" s="24"/>
-      <c r="AA15" s="24"/>
-      <c r="AB15" s="24"/>
-      <c r="AC15" s="24"/>
-      <c r="AD15" s="24"/>
-      <c r="AE15" s="24"/>
-      <c r="AF15" s="24"/>
-      <c r="AG15" s="24"/>
-      <c r="AH15" s="24"/>
-      <c r="AI15" s="24"/>
-      <c r="AJ15" s="24"/>
-      <c r="AK15" s="24"/>
-      <c r="AL15" s="24"/>
-      <c r="AM15" s="24"/>
-      <c r="AN15" s="29" t="str">
+      <c r="C15" s="18">
+        <v>1</v>
+      </c>
+      <c r="D15" s="19">
+        <v>45930</v>
+      </c>
+      <c r="E15" s="19">
+        <v>45946</v>
+      </c>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="R15" s="17"/>
+      <c r="S15" s="17"/>
+      <c r="T15" s="17"/>
+      <c r="U15" s="17"/>
+      <c r="V15" s="17"/>
+      <c r="W15" s="17"/>
+      <c r="X15" s="17"/>
+      <c r="Y15" s="17"/>
+      <c r="Z15" s="17"/>
+      <c r="AA15" s="17"/>
+      <c r="AB15" s="17"/>
+      <c r="AC15" s="17"/>
+      <c r="AD15" s="17"/>
+      <c r="AE15" s="17"/>
+      <c r="AF15" s="17"/>
+      <c r="AG15" s="17"/>
+      <c r="AH15" s="17"/>
+      <c r="AI15" s="17"/>
+      <c r="AJ15" s="17"/>
+      <c r="AK15" s="17"/>
+      <c r="AL15" s="17"/>
+      <c r="AM15" s="17"/>
+      <c r="AN15" s="22" t="str">
         <f>HYPERLINK("https://docs.google.com/document/d/1l_aqKtCJPsdabZFM-x0XuH-Zho9497SBj7Mbm_PzuVo/edit?usp=drive_link","Abrir")</f>
         <v>Abrir</v>
       </c>
     </row>
-    <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="24" t="s">
+    <row r="16" spans="1:40" ht="14.25" customHeight="1">
+      <c r="A16" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="25">
-        <v>1.0</v>
-      </c>
-      <c r="D16" s="26">
-        <v>45930.0</v>
-      </c>
-      <c r="E16" s="26">
-        <v>45945.0</v>
-      </c>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="24"/>
-      <c r="K16" s="24"/>
-      <c r="L16" s="24"/>
-      <c r="M16" s="24"/>
-      <c r="N16" s="24"/>
-      <c r="O16" s="24"/>
-      <c r="P16" s="24"/>
-      <c r="Q16" s="24"/>
-      <c r="R16" s="24"/>
-      <c r="S16" s="24"/>
-      <c r="T16" s="24"/>
-      <c r="U16" s="24"/>
-      <c r="V16" s="24"/>
-      <c r="W16" s="24"/>
-      <c r="X16" s="24"/>
-      <c r="Y16" s="24"/>
-      <c r="Z16" s="24"/>
-      <c r="AA16" s="24"/>
-      <c r="AB16" s="24"/>
-      <c r="AC16" s="24"/>
-      <c r="AD16" s="24"/>
-      <c r="AE16" s="24"/>
-      <c r="AF16" s="24"/>
-      <c r="AG16" s="24"/>
-      <c r="AH16" s="24"/>
-      <c r="AI16" s="24"/>
-      <c r="AJ16" s="24"/>
-      <c r="AK16" s="24"/>
-      <c r="AL16" s="24"/>
-      <c r="AM16" s="24"/>
-      <c r="AN16" s="29" t="str">
+      <c r="C16" s="18">
+        <v>1</v>
+      </c>
+      <c r="D16" s="19">
+        <v>45930</v>
+      </c>
+      <c r="E16" s="19">
+        <v>45945</v>
+      </c>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="17"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="17"/>
+      <c r="R16" s="17"/>
+      <c r="S16" s="17"/>
+      <c r="T16" s="17"/>
+      <c r="U16" s="17"/>
+      <c r="V16" s="17"/>
+      <c r="W16" s="17"/>
+      <c r="X16" s="17"/>
+      <c r="Y16" s="17"/>
+      <c r="Z16" s="17"/>
+      <c r="AA16" s="17"/>
+      <c r="AB16" s="17"/>
+      <c r="AC16" s="17"/>
+      <c r="AD16" s="17"/>
+      <c r="AE16" s="17"/>
+      <c r="AF16" s="17"/>
+      <c r="AG16" s="17"/>
+      <c r="AH16" s="17"/>
+      <c r="AI16" s="17"/>
+      <c r="AJ16" s="17"/>
+      <c r="AK16" s="17"/>
+      <c r="AL16" s="17"/>
+      <c r="AM16" s="17"/>
+      <c r="AN16" s="22" t="str">
         <f>HYPERLINK("https://docs.google.com/document/d/1tRtGj1mpXryeV61zUHXNDtCtZWrO7D2xm16uy9CMZ-4/edit?usp=drive_link","Abrir")</f>
         <v>Abrir</v>
       </c>
     </row>
-    <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="24" t="s">
+    <row r="17" spans="1:40" ht="14.25" customHeight="1">
+      <c r="A17" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="25">
-        <v>1.0</v>
-      </c>
-      <c r="D17" s="26">
-        <v>45930.0</v>
-      </c>
-      <c r="E17" s="26">
-        <v>45947.0</v>
-      </c>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="24"/>
-      <c r="K17" s="24"/>
-      <c r="L17" s="24"/>
-      <c r="M17" s="24"/>
-      <c r="N17" s="24"/>
-      <c r="O17" s="24"/>
-      <c r="P17" s="24"/>
-      <c r="Q17" s="24"/>
-      <c r="R17" s="24"/>
-      <c r="S17" s="24"/>
-      <c r="T17" s="24"/>
-      <c r="U17" s="24"/>
-      <c r="V17" s="24"/>
-      <c r="W17" s="24"/>
-      <c r="X17" s="24"/>
-      <c r="Y17" s="24"/>
-      <c r="Z17" s="24"/>
-      <c r="AA17" s="24"/>
-      <c r="AB17" s="24"/>
-      <c r="AC17" s="24"/>
-      <c r="AD17" s="24"/>
-      <c r="AE17" s="24"/>
-      <c r="AF17" s="24"/>
-      <c r="AG17" s="24"/>
-      <c r="AH17" s="24"/>
-      <c r="AI17" s="24"/>
-      <c r="AJ17" s="24"/>
-      <c r="AK17" s="24"/>
-      <c r="AL17" s="24"/>
-      <c r="AM17" s="24"/>
-      <c r="AN17" s="29" t="str">
+      <c r="C17" s="18">
+        <v>1</v>
+      </c>
+      <c r="D17" s="19">
+        <v>45930</v>
+      </c>
+      <c r="E17" s="19">
+        <v>45947</v>
+      </c>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="17"/>
+      <c r="R17" s="17"/>
+      <c r="S17" s="17"/>
+      <c r="T17" s="17"/>
+      <c r="U17" s="17"/>
+      <c r="V17" s="17"/>
+      <c r="W17" s="17"/>
+      <c r="X17" s="17"/>
+      <c r="Y17" s="17"/>
+      <c r="Z17" s="17"/>
+      <c r="AA17" s="17"/>
+      <c r="AB17" s="17"/>
+      <c r="AC17" s="17"/>
+      <c r="AD17" s="17"/>
+      <c r="AE17" s="17"/>
+      <c r="AF17" s="17"/>
+      <c r="AG17" s="17"/>
+      <c r="AH17" s="17"/>
+      <c r="AI17" s="17"/>
+      <c r="AJ17" s="17"/>
+      <c r="AK17" s="17"/>
+      <c r="AL17" s="17"/>
+      <c r="AM17" s="17"/>
+      <c r="AN17" s="22" t="str">
         <f>HYPERLINK("https://docs.google.com/presentation/d/1fJAplKSJ7NqUyvCXxRwpEFxBiNjIPOKG/edit?usp=drive_link&amp;ouid=111566450765270646432&amp;rtpof=true&amp;sd=true","Abrir")</f>
         <v>Abrir</v>
       </c>
     </row>
-    <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="23" t="s">
+    <row r="18" spans="1:40" ht="14.25" customHeight="1">
+      <c r="A18" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="24"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="24"/>
-      <c r="J18" s="24"/>
-      <c r="K18" s="24"/>
-      <c r="L18" s="24"/>
-      <c r="M18" s="24"/>
-      <c r="N18" s="24"/>
-      <c r="O18" s="24"/>
-      <c r="P18" s="24"/>
-      <c r="Q18" s="24"/>
-      <c r="R18" s="24"/>
-      <c r="S18" s="24"/>
-      <c r="T18" s="24"/>
-      <c r="U18" s="24"/>
-      <c r="V18" s="24"/>
-      <c r="W18" s="24"/>
-      <c r="X18" s="24"/>
-      <c r="Y18" s="24"/>
-      <c r="Z18" s="24"/>
-      <c r="AA18" s="24"/>
-      <c r="AB18" s="24"/>
-      <c r="AC18" s="24"/>
-      <c r="AD18" s="24"/>
-      <c r="AE18" s="24"/>
-      <c r="AF18" s="24"/>
-      <c r="AG18" s="24"/>
-      <c r="AH18" s="24"/>
-      <c r="AI18" s="24"/>
-      <c r="AJ18" s="24"/>
-      <c r="AK18" s="24"/>
-      <c r="AL18" s="24"/>
-      <c r="AM18" s="24"/>
-      <c r="AN18" s="27"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="17"/>
+      <c r="M18" s="17"/>
+      <c r="N18" s="17"/>
+      <c r="O18" s="17"/>
+      <c r="P18" s="17"/>
+      <c r="Q18" s="17"/>
+      <c r="R18" s="17"/>
+      <c r="S18" s="17"/>
+      <c r="T18" s="17"/>
+      <c r="U18" s="17"/>
+      <c r="V18" s="17"/>
+      <c r="W18" s="17"/>
+      <c r="X18" s="17"/>
+      <c r="Y18" s="17"/>
+      <c r="Z18" s="17"/>
+      <c r="AA18" s="17"/>
+      <c r="AB18" s="17"/>
+      <c r="AC18" s="17"/>
+      <c r="AD18" s="17"/>
+      <c r="AE18" s="17"/>
+      <c r="AF18" s="17"/>
+      <c r="AG18" s="17"/>
+      <c r="AH18" s="17"/>
+      <c r="AI18" s="17"/>
+      <c r="AJ18" s="17"/>
+      <c r="AK18" s="17"/>
+      <c r="AL18" s="17"/>
+      <c r="AM18" s="17"/>
+      <c r="AN18" s="20"/>
     </row>
-    <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="24" t="s">
+    <row r="19" spans="1:40" ht="14.25" customHeight="1">
+      <c r="A19" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="24" t="s">
+      <c r="B19" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="25">
-        <v>1.0</v>
-      </c>
-      <c r="D19" s="26">
-        <v>45930.0</v>
-      </c>
-      <c r="E19" s="26">
-        <v>45947.0</v>
-      </c>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="24"/>
-      <c r="I19" s="24"/>
-      <c r="J19" s="24"/>
-      <c r="K19" s="24"/>
-      <c r="L19" s="24"/>
-      <c r="M19" s="24"/>
-      <c r="N19" s="24"/>
-      <c r="O19" s="24"/>
-      <c r="P19" s="24"/>
-      <c r="Q19" s="24"/>
-      <c r="R19" s="24"/>
-      <c r="S19" s="24"/>
-      <c r="T19" s="24"/>
-      <c r="U19" s="24"/>
-      <c r="V19" s="24"/>
-      <c r="W19" s="24"/>
-      <c r="X19" s="24"/>
-      <c r="Y19" s="24"/>
-      <c r="Z19" s="24"/>
-      <c r="AA19" s="24"/>
-      <c r="AB19" s="24"/>
-      <c r="AC19" s="24"/>
-      <c r="AD19" s="24"/>
-      <c r="AE19" s="24"/>
-      <c r="AF19" s="24"/>
-      <c r="AG19" s="24"/>
-      <c r="AH19" s="24"/>
-      <c r="AI19" s="24"/>
-      <c r="AJ19" s="24"/>
-      <c r="AK19" s="24"/>
-      <c r="AL19" s="24"/>
-      <c r="AM19" s="24"/>
-      <c r="AN19" s="29" t="str">
+      <c r="C19" s="18">
+        <v>1</v>
+      </c>
+      <c r="D19" s="19">
+        <v>45930</v>
+      </c>
+      <c r="E19" s="19">
+        <v>45947</v>
+      </c>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="17"/>
+      <c r="M19" s="17"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="17"/>
+      <c r="R19" s="17"/>
+      <c r="S19" s="17"/>
+      <c r="T19" s="17"/>
+      <c r="U19" s="17"/>
+      <c r="V19" s="17"/>
+      <c r="W19" s="17"/>
+      <c r="X19" s="17"/>
+      <c r="Y19" s="17"/>
+      <c r="Z19" s="17"/>
+      <c r="AA19" s="17"/>
+      <c r="AB19" s="17"/>
+      <c r="AC19" s="17"/>
+      <c r="AD19" s="17"/>
+      <c r="AE19" s="17"/>
+      <c r="AF19" s="17"/>
+      <c r="AG19" s="17"/>
+      <c r="AH19" s="17"/>
+      <c r="AI19" s="17"/>
+      <c r="AJ19" s="17"/>
+      <c r="AK19" s="17"/>
+      <c r="AL19" s="17"/>
+      <c r="AM19" s="17"/>
+      <c r="AN19" s="22" t="str">
         <f>HYPERLINK("https://docs.google.com/document/d/1bJYhatuAPab0Ewmku8t6_SVMUR_JHSAt/edit?usp=drive_link&amp;ouid=111566450765270646432&amp;rtpof=true&amp;sd=true","Abrir")</f>
         <v>Abrir</v>
       </c>
     </row>
-    <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="24" t="s">
+    <row r="20" spans="1:40" ht="14.25" customHeight="1">
+      <c r="A20" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="24" t="s">
+      <c r="B20" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="25">
-        <v>1.0</v>
-      </c>
-      <c r="D20" s="26">
-        <v>45930.0</v>
-      </c>
-      <c r="E20" s="26">
-        <v>45939.0</v>
-      </c>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="24"/>
-      <c r="I20" s="24"/>
-      <c r="J20" s="24"/>
-      <c r="K20" s="24"/>
-      <c r="L20" s="24"/>
-      <c r="M20" s="24"/>
-      <c r="N20" s="24"/>
-      <c r="O20" s="24"/>
-      <c r="P20" s="24"/>
-      <c r="Q20" s="24"/>
-      <c r="R20" s="24"/>
-      <c r="S20" s="24"/>
-      <c r="T20" s="24"/>
-      <c r="U20" s="24"/>
-      <c r="V20" s="24"/>
-      <c r="W20" s="24"/>
-      <c r="X20" s="24"/>
-      <c r="Y20" s="24"/>
-      <c r="Z20" s="24"/>
-      <c r="AA20" s="24"/>
-      <c r="AB20" s="24"/>
-      <c r="AC20" s="24"/>
-      <c r="AD20" s="24"/>
-      <c r="AE20" s="24"/>
-      <c r="AF20" s="24"/>
-      <c r="AG20" s="24"/>
-      <c r="AH20" s="24"/>
-      <c r="AI20" s="24"/>
-      <c r="AJ20" s="24"/>
-      <c r="AK20" s="24"/>
-      <c r="AL20" s="24"/>
-      <c r="AM20" s="24"/>
-      <c r="AN20" s="29" t="str">
+      <c r="C20" s="18">
+        <v>1</v>
+      </c>
+      <c r="D20" s="19">
+        <v>45930</v>
+      </c>
+      <c r="E20" s="19">
+        <v>45939</v>
+      </c>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="17"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="17"/>
+      <c r="R20" s="17"/>
+      <c r="S20" s="17"/>
+      <c r="T20" s="17"/>
+      <c r="U20" s="17"/>
+      <c r="V20" s="17"/>
+      <c r="W20" s="17"/>
+      <c r="X20" s="17"/>
+      <c r="Y20" s="17"/>
+      <c r="Z20" s="17"/>
+      <c r="AA20" s="17"/>
+      <c r="AB20" s="17"/>
+      <c r="AC20" s="17"/>
+      <c r="AD20" s="17"/>
+      <c r="AE20" s="17"/>
+      <c r="AF20" s="17"/>
+      <c r="AG20" s="17"/>
+      <c r="AH20" s="17"/>
+      <c r="AI20" s="17"/>
+      <c r="AJ20" s="17"/>
+      <c r="AK20" s="17"/>
+      <c r="AL20" s="17"/>
+      <c r="AM20" s="17"/>
+      <c r="AN20" s="22" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1MTn7lr__xPnT93TTZHy8_TIP_59zffzJ/view?usp=drive_link","Abrir")</f>
         <v>Abrir</v>
       </c>
     </row>
-    <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="24" t="s">
+    <row r="21" spans="1:40" ht="14.25" customHeight="1">
+      <c r="A21" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="25">
-        <v>1.0</v>
-      </c>
-      <c r="D21" s="26">
-        <v>45930.0</v>
-      </c>
-      <c r="E21" s="26">
-        <v>45935.0</v>
-      </c>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="24"/>
-      <c r="K21" s="24"/>
-      <c r="L21" s="24"/>
-      <c r="M21" s="24"/>
-      <c r="N21" s="24"/>
-      <c r="O21" s="24"/>
-      <c r="P21" s="24"/>
-      <c r="Q21" s="24"/>
-      <c r="R21" s="24"/>
-      <c r="S21" s="24"/>
-      <c r="T21" s="24"/>
-      <c r="U21" s="24"/>
-      <c r="V21" s="24"/>
-      <c r="W21" s="24"/>
-      <c r="X21" s="24"/>
-      <c r="Y21" s="24"/>
-      <c r="Z21" s="24"/>
-      <c r="AA21" s="24"/>
-      <c r="AB21" s="24"/>
-      <c r="AC21" s="24"/>
-      <c r="AD21" s="24"/>
-      <c r="AE21" s="24"/>
-      <c r="AF21" s="24"/>
-      <c r="AG21" s="24"/>
-      <c r="AH21" s="24"/>
-      <c r="AI21" s="24"/>
-      <c r="AJ21" s="24"/>
-      <c r="AK21" s="24"/>
-      <c r="AL21" s="24"/>
-      <c r="AM21" s="24"/>
-      <c r="AN21" s="29" t="str">
+      <c r="C21" s="18">
+        <v>1</v>
+      </c>
+      <c r="D21" s="19">
+        <v>45930</v>
+      </c>
+      <c r="E21" s="19">
+        <v>45940</v>
+      </c>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="17"/>
+      <c r="M21" s="17"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="17"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="17"/>
+      <c r="R21" s="17"/>
+      <c r="S21" s="17"/>
+      <c r="T21" s="17"/>
+      <c r="U21" s="17"/>
+      <c r="V21" s="17"/>
+      <c r="W21" s="17"/>
+      <c r="X21" s="17"/>
+      <c r="Y21" s="17"/>
+      <c r="Z21" s="17"/>
+      <c r="AA21" s="17"/>
+      <c r="AB21" s="17"/>
+      <c r="AC21" s="17"/>
+      <c r="AD21" s="17"/>
+      <c r="AE21" s="17"/>
+      <c r="AF21" s="17"/>
+      <c r="AG21" s="17"/>
+      <c r="AH21" s="17"/>
+      <c r="AI21" s="17"/>
+      <c r="AJ21" s="17"/>
+      <c r="AK21" s="17"/>
+      <c r="AL21" s="17"/>
+      <c r="AM21" s="17"/>
+      <c r="AN21" s="22" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1nKw4LvfcDFEqvlNkR5govyIFOheuEbMK/view?usp=drive_link","Abrir")</f>
         <v>Abrir</v>
       </c>
     </row>
-    <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="24" t="s">
+    <row r="22" spans="1:40" ht="14.25" customHeight="1">
+      <c r="A22" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C22" s="25">
-        <v>1.0</v>
-      </c>
-      <c r="D22" s="26">
-        <v>45930.0</v>
-      </c>
-      <c r="E22" s="26">
-        <v>45934.0</v>
-      </c>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="24"/>
-      <c r="I22" s="24"/>
-      <c r="J22" s="24"/>
-      <c r="K22" s="24"/>
-      <c r="L22" s="24"/>
-      <c r="M22" s="24"/>
-      <c r="N22" s="24"/>
-      <c r="O22" s="24"/>
-      <c r="P22" s="24"/>
-      <c r="Q22" s="24"/>
-      <c r="R22" s="24"/>
-      <c r="S22" s="24"/>
-      <c r="T22" s="24"/>
-      <c r="U22" s="24"/>
-      <c r="V22" s="24"/>
-      <c r="W22" s="24"/>
-      <c r="X22" s="24"/>
-      <c r="Y22" s="24"/>
-      <c r="Z22" s="24"/>
-      <c r="AA22" s="24"/>
-      <c r="AB22" s="24"/>
-      <c r="AC22" s="24"/>
-      <c r="AD22" s="24"/>
-      <c r="AE22" s="24"/>
-      <c r="AF22" s="24"/>
-      <c r="AG22" s="24"/>
-      <c r="AH22" s="24"/>
-      <c r="AI22" s="24"/>
-      <c r="AJ22" s="24"/>
-      <c r="AK22" s="24"/>
-      <c r="AL22" s="24"/>
-      <c r="AM22" s="24"/>
-      <c r="AN22" s="29" t="str">
+      <c r="C22" s="18">
+        <v>1</v>
+      </c>
+      <c r="D22" s="19">
+        <v>45930</v>
+      </c>
+      <c r="E22" s="19">
+        <v>45935</v>
+      </c>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="17"/>
+      <c r="M22" s="17"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="17"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="17"/>
+      <c r="R22" s="17"/>
+      <c r="S22" s="17"/>
+      <c r="T22" s="17"/>
+      <c r="U22" s="17"/>
+      <c r="V22" s="17"/>
+      <c r="W22" s="17"/>
+      <c r="X22" s="17"/>
+      <c r="Y22" s="17"/>
+      <c r="Z22" s="17"/>
+      <c r="AA22" s="17"/>
+      <c r="AB22" s="17"/>
+      <c r="AC22" s="17"/>
+      <c r="AD22" s="17"/>
+      <c r="AE22" s="17"/>
+      <c r="AF22" s="17"/>
+      <c r="AG22" s="17"/>
+      <c r="AH22" s="17"/>
+      <c r="AI22" s="17"/>
+      <c r="AJ22" s="17"/>
+      <c r="AK22" s="17"/>
+      <c r="AL22" s="17"/>
+      <c r="AM22" s="17"/>
+      <c r="AN22" s="22" t="str">
         <f>HYPERLINK("https://drive.google.com/file/d/1SaVtUASrkL8TgJY1wVSMPzNyszZgRYIb/view?usp=drive_link","Abrir")</f>
         <v>Abrir</v>
       </c>
     </row>
-    <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="30"/>
-      <c r="B23" s="30"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="30"/>
-      <c r="I23" s="30"/>
-      <c r="J23" s="30"/>
-      <c r="K23" s="30"/>
-      <c r="L23" s="30"/>
-      <c r="M23" s="30"/>
-      <c r="N23" s="30"/>
-      <c r="O23" s="30"/>
-      <c r="P23" s="30"/>
-      <c r="Q23" s="30"/>
-      <c r="R23" s="30"/>
-      <c r="S23" s="30"/>
-      <c r="T23" s="30"/>
-      <c r="U23" s="30"/>
-      <c r="V23" s="30"/>
-      <c r="W23" s="30"/>
-      <c r="X23" s="30"/>
-      <c r="Y23" s="30"/>
-      <c r="Z23" s="30"/>
-      <c r="AA23" s="30"/>
-      <c r="AB23" s="30"/>
-      <c r="AC23" s="30"/>
-      <c r="AD23" s="30"/>
-      <c r="AE23" s="30"/>
-      <c r="AF23" s="30"/>
-      <c r="AG23" s="30"/>
-      <c r="AH23" s="30"/>
-      <c r="AI23" s="30"/>
-      <c r="AJ23" s="30"/>
-      <c r="AK23" s="30"/>
-      <c r="AL23" s="30"/>
-      <c r="AM23" s="30"/>
+    <row r="23" spans="1:40" ht="14.25" customHeight="1">
+      <c r="A23" s="23"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="23"/>
+      <c r="K23" s="23"/>
+      <c r="L23" s="23"/>
+      <c r="M23" s="23"/>
+      <c r="N23" s="23"/>
+      <c r="O23" s="23"/>
+      <c r="P23" s="23"/>
+      <c r="Q23" s="23"/>
+      <c r="R23" s="23"/>
+      <c r="S23" s="23"/>
+      <c r="T23" s="23"/>
+      <c r="U23" s="23"/>
+      <c r="V23" s="23"/>
+      <c r="W23" s="23"/>
+      <c r="X23" s="23"/>
+      <c r="Y23" s="23"/>
+      <c r="Z23" s="23"/>
+      <c r="AA23" s="23"/>
+      <c r="AB23" s="23"/>
+      <c r="AC23" s="23"/>
+      <c r="AD23" s="23"/>
+      <c r="AE23" s="23"/>
+      <c r="AF23" s="23"/>
+      <c r="AG23" s="23"/>
+      <c r="AH23" s="23"/>
+      <c r="AI23" s="23"/>
+      <c r="AJ23" s="23"/>
+      <c r="AK23" s="23"/>
+      <c r="AL23" s="23"/>
+      <c r="AM23" s="23"/>
     </row>
-    <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="33"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="35"/>
+    <row r="24" spans="1:40" ht="14.25" customHeight="1">
+      <c r="A24" s="26"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="28"/>
     </row>
-    <row r="25" ht="14.25" customHeight="1">
-      <c r="D25" s="35"/>
-      <c r="E25" s="35"/>
+    <row r="25" spans="1:40" ht="14.25" customHeight="1">
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
     </row>
-    <row r="26" ht="14.25" customHeight="1"/>
-    <row r="27" ht="14.25" customHeight="1"/>
-    <row r="28" ht="14.25" customHeight="1"/>
-    <row r="29" ht="14.25" customHeight="1"/>
-    <row r="30" ht="14.25" customHeight="1"/>
-    <row r="31" ht="14.25" customHeight="1"/>
-    <row r="32" ht="14.25" customHeight="1">
-      <c r="D32" s="36"/>
+    <row r="26" spans="1:40" ht="14.25" customHeight="1"/>
+    <row r="27" spans="1:40" ht="14.25" customHeight="1"/>
+    <row r="28" spans="1:40" ht="14.25" customHeight="1"/>
+    <row r="29" spans="1:40" ht="14.25" customHeight="1"/>
+    <row r="30" spans="1:40" ht="14.25" customHeight="1"/>
+    <row r="31" spans="1:40" ht="14.25" customHeight="1"/>
+    <row r="32" spans="1:40" ht="14.25" customHeight="1">
+      <c r="D32" s="29"/>
     </row>
     <row r="33" ht="14.25" customHeight="1"/>
     <row r="34" ht="14.25" customHeight="1"/>
@@ -2912,1256 +2986,1252 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="D5:E5"/>
     <mergeCell ref="G4:K4"/>
     <mergeCell ref="L4:R4"/>
     <mergeCell ref="S4:Y4"/>
     <mergeCell ref="Z4:AF4"/>
     <mergeCell ref="AG4:AM4"/>
-    <mergeCell ref="D5:E5"/>
   </mergeCells>
   <conditionalFormatting sqref="G7:AM23">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>AND(G$5&gt;=$D7,G$5&lt;=((($E7-$D7+1)*$C7)+$D7-1))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G7:AM23">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>AND(G$5&gt;=$D7,G$5&lt;=$E7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor rgb="FF4D94D8"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:AM1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="15.75"/>
-    <col customWidth="1" min="3" max="5" width="11.75"/>
-    <col customWidth="1" min="6" max="39" width="3.75"/>
+    <col min="1" max="2" width="15.77734375" customWidth="1"/>
+    <col min="3" max="5" width="11.77734375" customWidth="1"/>
+    <col min="6" max="39" width="3.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1"/>
-    <row r="2" ht="14.25" customHeight="1"/>
-    <row r="3" ht="14.25" customHeight="1"/>
-    <row r="4" ht="19.5" customHeight="1">
+    <row r="1" spans="1:39" ht="14.25" customHeight="1"/>
+    <row r="2" spans="1:39" ht="14.25" customHeight="1"/>
+    <row r="3" spans="1:39" ht="14.25" customHeight="1"/>
+    <row r="4" spans="1:39" ht="19.5" customHeight="1">
       <c r="D4" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2">
         <f>D5+D4</f>
         <v>45930</v>
       </c>
       <c r="F4" s="3"/>
-      <c r="G4" s="4">
+      <c r="G4" s="30">
         <f>G5</f>
         <v>45930</v>
       </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="4">
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="32"/>
+      <c r="L4" s="30">
         <f>L5</f>
         <v>45935</v>
       </c>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="4">
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
+      <c r="O4" s="31"/>
+      <c r="P4" s="31"/>
+      <c r="Q4" s="31"/>
+      <c r="R4" s="32"/>
+      <c r="S4" s="30">
         <f>S5</f>
         <v>45942</v>
       </c>
-      <c r="T4" s="5"/>
-      <c r="U4" s="5"/>
-      <c r="V4" s="5"/>
-      <c r="W4" s="5"/>
-      <c r="X4" s="5"/>
-      <c r="Y4" s="6"/>
-      <c r="Z4" s="4">
+      <c r="T4" s="31"/>
+      <c r="U4" s="31"/>
+      <c r="V4" s="31"/>
+      <c r="W4" s="31"/>
+      <c r="X4" s="31"/>
+      <c r="Y4" s="32"/>
+      <c r="Z4" s="30">
         <f>Z5</f>
         <v>45949</v>
       </c>
-      <c r="AA4" s="5"/>
-      <c r="AB4" s="5"/>
-      <c r="AC4" s="5"/>
-      <c r="AD4" s="5"/>
-      <c r="AE4" s="5"/>
-      <c r="AF4" s="6"/>
-      <c r="AG4" s="7">
+      <c r="AA4" s="31"/>
+      <c r="AB4" s="31"/>
+      <c r="AC4" s="31"/>
+      <c r="AD4" s="31"/>
+      <c r="AE4" s="31"/>
+      <c r="AF4" s="32"/>
+      <c r="AG4" s="33">
         <f>AG5</f>
         <v>45956</v>
       </c>
-      <c r="AH4" s="5"/>
-      <c r="AI4" s="5"/>
-      <c r="AJ4" s="5"/>
-      <c r="AK4" s="5"/>
-      <c r="AL4" s="5"/>
-      <c r="AM4" s="6"/>
+      <c r="AH4" s="31"/>
+      <c r="AI4" s="31"/>
+      <c r="AJ4" s="31"/>
+      <c r="AK4" s="31"/>
+      <c r="AL4" s="31"/>
+      <c r="AM4" s="32"/>
     </row>
-    <row r="5" ht="14.25" customHeight="1">
-      <c r="B5" s="10"/>
-      <c r="C5" s="11" t="s">
+    <row r="5" spans="1:39" ht="14.25" customHeight="1">
+      <c r="B5" s="5"/>
+      <c r="C5" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="35">
         <f>DATE(2025,10,1)+$D$4-1</f>
         <v>45930</v>
       </c>
-      <c r="E5" s="13"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="15">
+      <c r="E5" s="36"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="8">
         <f>D5</f>
         <v>45930</v>
       </c>
-      <c r="H5" s="16">
-        <f t="shared" ref="H5:AM5" si="1">G5+1</f>
+      <c r="H5" s="9">
+        <f t="shared" ref="H5:AM5" si="0">G5+1</f>
         <v>45931</v>
       </c>
-      <c r="I5" s="16">
-        <f t="shared" si="1"/>
+      <c r="I5" s="9">
+        <f t="shared" si="0"/>
         <v>45932</v>
       </c>
-      <c r="J5" s="16">
-        <f t="shared" si="1"/>
+      <c r="J5" s="9">
+        <f t="shared" si="0"/>
         <v>45933</v>
       </c>
-      <c r="K5" s="17">
-        <f t="shared" si="1"/>
+      <c r="K5" s="10">
+        <f t="shared" si="0"/>
         <v>45934</v>
       </c>
-      <c r="L5" s="15">
-        <f t="shared" si="1"/>
+      <c r="L5" s="8">
+        <f t="shared" si="0"/>
         <v>45935</v>
       </c>
-      <c r="M5" s="16">
-        <f t="shared" si="1"/>
+      <c r="M5" s="9">
+        <f t="shared" si="0"/>
         <v>45936</v>
       </c>
-      <c r="N5" s="16">
-        <f t="shared" si="1"/>
+      <c r="N5" s="9">
+        <f t="shared" si="0"/>
         <v>45937</v>
       </c>
-      <c r="O5" s="16">
-        <f t="shared" si="1"/>
+      <c r="O5" s="9">
+        <f t="shared" si="0"/>
         <v>45938</v>
       </c>
-      <c r="P5" s="16">
-        <f t="shared" si="1"/>
+      <c r="P5" s="9">
+        <f t="shared" si="0"/>
         <v>45939</v>
       </c>
-      <c r="Q5" s="16">
-        <f t="shared" si="1"/>
+      <c r="Q5" s="9">
+        <f t="shared" si="0"/>
         <v>45940</v>
       </c>
-      <c r="R5" s="17">
-        <f t="shared" si="1"/>
+      <c r="R5" s="10">
+        <f t="shared" si="0"/>
         <v>45941</v>
       </c>
-      <c r="S5" s="15">
-        <f t="shared" si="1"/>
+      <c r="S5" s="8">
+        <f t="shared" si="0"/>
         <v>45942</v>
       </c>
-      <c r="T5" s="16">
-        <f t="shared" si="1"/>
+      <c r="T5" s="9">
+        <f t="shared" si="0"/>
         <v>45943</v>
       </c>
-      <c r="U5" s="16">
-        <f t="shared" si="1"/>
+      <c r="U5" s="9">
+        <f t="shared" si="0"/>
         <v>45944</v>
       </c>
-      <c r="V5" s="16">
-        <f t="shared" si="1"/>
+      <c r="V5" s="9">
+        <f t="shared" si="0"/>
         <v>45945</v>
       </c>
-      <c r="W5" s="16">
-        <f t="shared" si="1"/>
+      <c r="W5" s="9">
+        <f t="shared" si="0"/>
         <v>45946</v>
       </c>
-      <c r="X5" s="16">
-        <f t="shared" si="1"/>
+      <c r="X5" s="9">
+        <f t="shared" si="0"/>
         <v>45947</v>
       </c>
-      <c r="Y5" s="17">
-        <f t="shared" si="1"/>
+      <c r="Y5" s="10">
+        <f t="shared" si="0"/>
         <v>45948</v>
       </c>
-      <c r="Z5" s="15">
-        <f t="shared" si="1"/>
+      <c r="Z5" s="8">
+        <f t="shared" si="0"/>
         <v>45949</v>
       </c>
-      <c r="AA5" s="16">
-        <f t="shared" si="1"/>
+      <c r="AA5" s="9">
+        <f t="shared" si="0"/>
         <v>45950</v>
       </c>
-      <c r="AB5" s="16">
-        <f t="shared" si="1"/>
+      <c r="AB5" s="9">
+        <f t="shared" si="0"/>
         <v>45951</v>
       </c>
-      <c r="AC5" s="16">
-        <f t="shared" si="1"/>
+      <c r="AC5" s="9">
+        <f t="shared" si="0"/>
         <v>45952</v>
       </c>
-      <c r="AD5" s="16">
-        <f t="shared" si="1"/>
+      <c r="AD5" s="9">
+        <f t="shared" si="0"/>
         <v>45953</v>
       </c>
-      <c r="AE5" s="16">
-        <f t="shared" si="1"/>
+      <c r="AE5" s="9">
+        <f t="shared" si="0"/>
         <v>45954</v>
       </c>
-      <c r="AF5" s="17">
-        <f t="shared" si="1"/>
+      <c r="AF5" s="10">
+        <f t="shared" si="0"/>
         <v>45955</v>
       </c>
-      <c r="AG5" s="16">
-        <f t="shared" si="1"/>
+      <c r="AG5" s="9">
+        <f t="shared" si="0"/>
         <v>45956</v>
       </c>
-      <c r="AH5" s="16">
-        <f t="shared" si="1"/>
+      <c r="AH5" s="9">
+        <f t="shared" si="0"/>
         <v>45957</v>
       </c>
-      <c r="AI5" s="16">
-        <f t="shared" si="1"/>
+      <c r="AI5" s="9">
+        <f t="shared" si="0"/>
         <v>45958</v>
       </c>
-      <c r="AJ5" s="16">
-        <f t="shared" si="1"/>
+      <c r="AJ5" s="9">
+        <f t="shared" si="0"/>
         <v>45959</v>
       </c>
-      <c r="AK5" s="16">
-        <f t="shared" si="1"/>
+      <c r="AK5" s="9">
+        <f t="shared" si="0"/>
         <v>45960</v>
       </c>
-      <c r="AL5" s="16">
-        <f t="shared" si="1"/>
+      <c r="AL5" s="9">
+        <f t="shared" si="0"/>
         <v>45961</v>
       </c>
-      <c r="AM5" s="17">
-        <f t="shared" si="1"/>
+      <c r="AM5" s="10">
+        <f t="shared" si="0"/>
         <v>45962</v>
       </c>
     </row>
-    <row r="6" ht="19.5" customHeight="1">
-      <c r="A6" s="19" t="s">
+    <row r="6" spans="1:39" ht="19.5" customHeight="1">
+      <c r="A6" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="20"/>
-      <c r="G6" s="21" t="str">
-        <f t="shared" ref="G6:AM6" si="2">UPPER(LEFT(TEXT(G5,"ddd"),1))</f>
+      <c r="F6" s="13"/>
+      <c r="G6" s="14" t="str">
+        <f t="shared" ref="G6:AM6" si="1">UPPER(LEFT(TEXT(G5,"ddd"),1))</f>
         <v>M</v>
       </c>
-      <c r="H6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="H6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>M</v>
       </c>
-      <c r="I6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="I6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>J</v>
       </c>
-      <c r="J6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="J6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>V</v>
       </c>
-      <c r="K6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="K6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>S</v>
       </c>
-      <c r="L6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="L6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>D</v>
       </c>
-      <c r="M6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="M6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="N6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="N6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>M</v>
       </c>
-      <c r="O6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="O6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>M</v>
       </c>
-      <c r="P6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="P6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>J</v>
       </c>
-      <c r="Q6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="Q6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>V</v>
       </c>
-      <c r="R6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="R6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>S</v>
       </c>
-      <c r="S6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="S6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>D</v>
       </c>
-      <c r="T6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="T6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="U6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="U6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>M</v>
       </c>
-      <c r="V6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="V6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>M</v>
       </c>
-      <c r="W6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="W6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>J</v>
       </c>
-      <c r="X6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="X6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>V</v>
       </c>
-      <c r="Y6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="Y6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>S</v>
       </c>
-      <c r="Z6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="Z6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>D</v>
       </c>
-      <c r="AA6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="AA6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="AB6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="AB6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>M</v>
       </c>
-      <c r="AC6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="AC6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>M</v>
       </c>
-      <c r="AD6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="AD6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>J</v>
       </c>
-      <c r="AE6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="AE6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>V</v>
       </c>
-      <c r="AF6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="AF6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>S</v>
       </c>
-      <c r="AG6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="AG6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>D</v>
       </c>
-      <c r="AH6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="AH6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>L</v>
       </c>
-      <c r="AI6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="AI6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>M</v>
       </c>
-      <c r="AJ6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="AJ6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>M</v>
       </c>
-      <c r="AK6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="AK6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>J</v>
       </c>
-      <c r="AL6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="AL6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>V</v>
       </c>
-      <c r="AM6" s="21" t="str">
-        <f t="shared" si="2"/>
+      <c r="AM6" s="14" t="str">
+        <f t="shared" si="1"/>
         <v>S</v>
       </c>
     </row>
-    <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="23" t="s">
+    <row r="7" spans="1:39" ht="14.25" customHeight="1">
+      <c r="A7" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="24"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="24"/>
-      <c r="N7" s="24"/>
-      <c r="O7" s="24"/>
-      <c r="P7" s="24"/>
-      <c r="Q7" s="24"/>
-      <c r="R7" s="24"/>
-      <c r="S7" s="24"/>
-      <c r="T7" s="24"/>
-      <c r="U7" s="24"/>
-      <c r="V7" s="24"/>
-      <c r="W7" s="24"/>
-      <c r="X7" s="24"/>
-      <c r="Y7" s="24"/>
-      <c r="Z7" s="24"/>
-      <c r="AA7" s="24"/>
-      <c r="AB7" s="24"/>
-      <c r="AC7" s="24"/>
-      <c r="AD7" s="24"/>
-      <c r="AE7" s="24"/>
-      <c r="AF7" s="24"/>
-      <c r="AG7" s="24"/>
-      <c r="AH7" s="24"/>
-      <c r="AI7" s="24"/>
-      <c r="AJ7" s="24"/>
-      <c r="AK7" s="24"/>
-      <c r="AL7" s="24"/>
-      <c r="AM7" s="24"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="17"/>
+      <c r="Q7" s="17"/>
+      <c r="R7" s="17"/>
+      <c r="S7" s="17"/>
+      <c r="T7" s="17"/>
+      <c r="U7" s="17"/>
+      <c r="V7" s="17"/>
+      <c r="W7" s="17"/>
+      <c r="X7" s="17"/>
+      <c r="Y7" s="17"/>
+      <c r="Z7" s="17"/>
+      <c r="AA7" s="17"/>
+      <c r="AB7" s="17"/>
+      <c r="AC7" s="17"/>
+      <c r="AD7" s="17"/>
+      <c r="AE7" s="17"/>
+      <c r="AF7" s="17"/>
+      <c r="AG7" s="17"/>
+      <c r="AH7" s="17"/>
+      <c r="AI7" s="17"/>
+      <c r="AJ7" s="17"/>
+      <c r="AK7" s="17"/>
+      <c r="AL7" s="17"/>
+      <c r="AM7" s="17"/>
     </row>
-    <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="24" t="s">
+    <row r="8" spans="1:39" ht="14.25" customHeight="1">
+      <c r="A8" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="18">
         <v>0.9</v>
       </c>
-      <c r="D8" s="26">
-        <v>45930.0</v>
-      </c>
-      <c r="E8" s="26">
-        <v>45943.0</v>
-      </c>
-      <c r="F8" s="24"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="24"/>
-      <c r="I8" s="24"/>
-      <c r="J8" s="24"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="24"/>
-      <c r="M8" s="24"/>
-      <c r="N8" s="24"/>
-      <c r="O8" s="24"/>
-      <c r="P8" s="24"/>
-      <c r="Q8" s="24"/>
-      <c r="R8" s="24"/>
-      <c r="S8" s="24"/>
-      <c r="T8" s="24"/>
-      <c r="U8" s="24"/>
-      <c r="V8" s="24"/>
-      <c r="W8" s="24"/>
-      <c r="X8" s="24"/>
-      <c r="Y8" s="24"/>
-      <c r="Z8" s="24"/>
-      <c r="AA8" s="24"/>
-      <c r="AB8" s="24"/>
-      <c r="AC8" s="24"/>
-      <c r="AD8" s="24"/>
-      <c r="AE8" s="24"/>
-      <c r="AF8" s="24"/>
-      <c r="AG8" s="24"/>
-      <c r="AH8" s="24"/>
-      <c r="AI8" s="24"/>
-      <c r="AJ8" s="24"/>
-      <c r="AK8" s="24"/>
-      <c r="AL8" s="24"/>
-      <c r="AM8" s="24"/>
+      <c r="D8" s="19">
+        <v>45930</v>
+      </c>
+      <c r="E8" s="19">
+        <v>45943</v>
+      </c>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="17"/>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="17"/>
+      <c r="R8" s="17"/>
+      <c r="S8" s="17"/>
+      <c r="T8" s="17"/>
+      <c r="U8" s="17"/>
+      <c r="V8" s="17"/>
+      <c r="W8" s="17"/>
+      <c r="X8" s="17"/>
+      <c r="Y8" s="17"/>
+      <c r="Z8" s="17"/>
+      <c r="AA8" s="17"/>
+      <c r="AB8" s="17"/>
+      <c r="AC8" s="17"/>
+      <c r="AD8" s="17"/>
+      <c r="AE8" s="17"/>
+      <c r="AF8" s="17"/>
+      <c r="AG8" s="17"/>
+      <c r="AH8" s="17"/>
+      <c r="AI8" s="17"/>
+      <c r="AJ8" s="17"/>
+      <c r="AK8" s="17"/>
+      <c r="AL8" s="17"/>
+      <c r="AM8" s="17"/>
     </row>
-    <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="24" t="s">
+    <row r="9" spans="1:39" ht="14.25" customHeight="1">
+      <c r="A9" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="25">
-        <v>1.0</v>
-      </c>
-      <c r="D9" s="26">
-        <v>45930.0</v>
-      </c>
-      <c r="E9" s="26">
-        <v>45942.0</v>
-      </c>
-      <c r="F9" s="24"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="24"/>
-      <c r="I9" s="24"/>
-      <c r="J9" s="24"/>
-      <c r="K9" s="24"/>
-      <c r="L9" s="24"/>
-      <c r="M9" s="24"/>
-      <c r="N9" s="24"/>
-      <c r="O9" s="24"/>
-      <c r="P9" s="24"/>
-      <c r="Q9" s="24"/>
-      <c r="R9" s="24"/>
-      <c r="S9" s="24"/>
-      <c r="T9" s="24"/>
-      <c r="U9" s="24"/>
-      <c r="V9" s="24"/>
-      <c r="W9" s="24"/>
-      <c r="X9" s="24"/>
-      <c r="Y9" s="24"/>
-      <c r="Z9" s="24"/>
-      <c r="AA9" s="24"/>
-      <c r="AB9" s="24"/>
-      <c r="AC9" s="24"/>
-      <c r="AD9" s="24"/>
-      <c r="AE9" s="24"/>
-      <c r="AF9" s="24"/>
-      <c r="AG9" s="24"/>
-      <c r="AH9" s="24"/>
-      <c r="AI9" s="24"/>
-      <c r="AJ9" s="24"/>
-      <c r="AK9" s="24"/>
-      <c r="AL9" s="24"/>
-      <c r="AM9" s="24"/>
+      <c r="C9" s="18">
+        <v>1</v>
+      </c>
+      <c r="D9" s="19">
+        <v>45930</v>
+      </c>
+      <c r="E9" s="19">
+        <v>45942</v>
+      </c>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17"/>
+      <c r="R9" s="17"/>
+      <c r="S9" s="17"/>
+      <c r="T9" s="17"/>
+      <c r="U9" s="17"/>
+      <c r="V9" s="17"/>
+      <c r="W9" s="17"/>
+      <c r="X9" s="17"/>
+      <c r="Y9" s="17"/>
+      <c r="Z9" s="17"/>
+      <c r="AA9" s="17"/>
+      <c r="AB9" s="17"/>
+      <c r="AC9" s="17"/>
+      <c r="AD9" s="17"/>
+      <c r="AE9" s="17"/>
+      <c r="AF9" s="17"/>
+      <c r="AG9" s="17"/>
+      <c r="AH9" s="17"/>
+      <c r="AI9" s="17"/>
+      <c r="AJ9" s="17"/>
+      <c r="AK9" s="17"/>
+      <c r="AL9" s="17"/>
+      <c r="AM9" s="17"/>
     </row>
-    <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="24" t="s">
+    <row r="10" spans="1:39" ht="14.25" customHeight="1">
+      <c r="A10" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="25">
-        <v>1.0</v>
-      </c>
-      <c r="D10" s="26">
-        <v>45930.0</v>
-      </c>
-      <c r="E10" s="26">
-        <v>45942.0</v>
-      </c>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="24"/>
-      <c r="M10" s="24"/>
-      <c r="N10" s="24"/>
-      <c r="O10" s="24"/>
-      <c r="P10" s="24"/>
-      <c r="Q10" s="24"/>
-      <c r="R10" s="24"/>
-      <c r="S10" s="24"/>
-      <c r="T10" s="24"/>
-      <c r="U10" s="24"/>
-      <c r="V10" s="24"/>
-      <c r="W10" s="24"/>
-      <c r="X10" s="24"/>
-      <c r="Y10" s="24"/>
-      <c r="Z10" s="24"/>
-      <c r="AA10" s="24"/>
-      <c r="AB10" s="24"/>
-      <c r="AC10" s="24"/>
-      <c r="AD10" s="24"/>
-      <c r="AE10" s="24"/>
-      <c r="AF10" s="24"/>
-      <c r="AG10" s="24"/>
-      <c r="AH10" s="24"/>
-      <c r="AI10" s="24"/>
-      <c r="AJ10" s="24"/>
-      <c r="AK10" s="24"/>
-      <c r="AL10" s="24"/>
-      <c r="AM10" s="24"/>
+      <c r="C10" s="18">
+        <v>1</v>
+      </c>
+      <c r="D10" s="19">
+        <v>45930</v>
+      </c>
+      <c r="E10" s="19">
+        <v>45942</v>
+      </c>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="17"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="17"/>
+      <c r="S10" s="17"/>
+      <c r="T10" s="17"/>
+      <c r="U10" s="17"/>
+      <c r="V10" s="17"/>
+      <c r="W10" s="17"/>
+      <c r="X10" s="17"/>
+      <c r="Y10" s="17"/>
+      <c r="Z10" s="17"/>
+      <c r="AA10" s="17"/>
+      <c r="AB10" s="17"/>
+      <c r="AC10" s="17"/>
+      <c r="AD10" s="17"/>
+      <c r="AE10" s="17"/>
+      <c r="AF10" s="17"/>
+      <c r="AG10" s="17"/>
+      <c r="AH10" s="17"/>
+      <c r="AI10" s="17"/>
+      <c r="AJ10" s="17"/>
+      <c r="AK10" s="17"/>
+      <c r="AL10" s="17"/>
+      <c r="AM10" s="17"/>
     </row>
-    <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="24" t="s">
+    <row r="11" spans="1:39" ht="14.25" customHeight="1">
+      <c r="A11" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="25">
-        <v>1.0</v>
-      </c>
-      <c r="D11" s="26">
-        <v>45930.0</v>
-      </c>
-      <c r="E11" s="26">
-        <v>45943.0</v>
-      </c>
-      <c r="F11" s="24"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="24"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="24"/>
-      <c r="K11" s="24"/>
-      <c r="L11" s="24"/>
-      <c r="M11" s="24"/>
-      <c r="N11" s="24"/>
-      <c r="O11" s="24"/>
-      <c r="P11" s="24"/>
-      <c r="Q11" s="24"/>
-      <c r="R11" s="24"/>
-      <c r="S11" s="24"/>
-      <c r="T11" s="24"/>
-      <c r="U11" s="24"/>
-      <c r="V11" s="24"/>
-      <c r="W11" s="24"/>
-      <c r="X11" s="24"/>
-      <c r="Y11" s="24"/>
-      <c r="Z11" s="24"/>
-      <c r="AA11" s="24"/>
-      <c r="AB11" s="24"/>
-      <c r="AC11" s="24"/>
-      <c r="AD11" s="24"/>
-      <c r="AE11" s="24"/>
-      <c r="AF11" s="24"/>
-      <c r="AG11" s="24"/>
-      <c r="AH11" s="24"/>
-      <c r="AI11" s="24"/>
-      <c r="AJ11" s="24"/>
-      <c r="AK11" s="24"/>
-      <c r="AL11" s="24"/>
-      <c r="AM11" s="24"/>
+      <c r="C11" s="18">
+        <v>1</v>
+      </c>
+      <c r="D11" s="19">
+        <v>45930</v>
+      </c>
+      <c r="E11" s="19">
+        <v>45943</v>
+      </c>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="17"/>
+      <c r="S11" s="17"/>
+      <c r="T11" s="17"/>
+      <c r="U11" s="17"/>
+      <c r="V11" s="17"/>
+      <c r="W11" s="17"/>
+      <c r="X11" s="17"/>
+      <c r="Y11" s="17"/>
+      <c r="Z11" s="17"/>
+      <c r="AA11" s="17"/>
+      <c r="AB11" s="17"/>
+      <c r="AC11" s="17"/>
+      <c r="AD11" s="17"/>
+      <c r="AE11" s="17"/>
+      <c r="AF11" s="17"/>
+      <c r="AG11" s="17"/>
+      <c r="AH11" s="17"/>
+      <c r="AI11" s="17"/>
+      <c r="AJ11" s="17"/>
+      <c r="AK11" s="17"/>
+      <c r="AL11" s="17"/>
+      <c r="AM11" s="17"/>
     </row>
-    <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="24" t="s">
+    <row r="12" spans="1:39" ht="14.25" customHeight="1">
+      <c r="A12" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="25">
-        <v>1.0</v>
-      </c>
-      <c r="D12" s="26">
-        <v>45930.0</v>
-      </c>
-      <c r="E12" s="26">
-        <v>45947.0</v>
-      </c>
-      <c r="F12" s="24"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="24"/>
-      <c r="I12" s="24"/>
-      <c r="J12" s="24"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="24"/>
-      <c r="M12" s="24"/>
-      <c r="N12" s="24"/>
-      <c r="O12" s="24"/>
-      <c r="P12" s="24"/>
-      <c r="Q12" s="24"/>
-      <c r="R12" s="24"/>
-      <c r="S12" s="24"/>
-      <c r="T12" s="24"/>
-      <c r="U12" s="24"/>
-      <c r="V12" s="24"/>
-      <c r="W12" s="24"/>
-      <c r="X12" s="24"/>
-      <c r="Y12" s="24"/>
-      <c r="Z12" s="24"/>
-      <c r="AA12" s="24"/>
-      <c r="AB12" s="24"/>
-      <c r="AC12" s="24"/>
-      <c r="AD12" s="24"/>
-      <c r="AE12" s="24"/>
-      <c r="AF12" s="24"/>
-      <c r="AG12" s="24"/>
-      <c r="AH12" s="24"/>
-      <c r="AI12" s="24"/>
-      <c r="AJ12" s="24"/>
-      <c r="AK12" s="24"/>
-      <c r="AL12" s="24"/>
-      <c r="AM12" s="24"/>
+      <c r="C12" s="18">
+        <v>1</v>
+      </c>
+      <c r="D12" s="19">
+        <v>45930</v>
+      </c>
+      <c r="E12" s="19">
+        <v>45947</v>
+      </c>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17"/>
+      <c r="R12" s="17"/>
+      <c r="S12" s="17"/>
+      <c r="T12" s="17"/>
+      <c r="U12" s="17"/>
+      <c r="V12" s="17"/>
+      <c r="W12" s="17"/>
+      <c r="X12" s="17"/>
+      <c r="Y12" s="17"/>
+      <c r="Z12" s="17"/>
+      <c r="AA12" s="17"/>
+      <c r="AB12" s="17"/>
+      <c r="AC12" s="17"/>
+      <c r="AD12" s="17"/>
+      <c r="AE12" s="17"/>
+      <c r="AF12" s="17"/>
+      <c r="AG12" s="17"/>
+      <c r="AH12" s="17"/>
+      <c r="AI12" s="17"/>
+      <c r="AJ12" s="17"/>
+      <c r="AK12" s="17"/>
+      <c r="AL12" s="17"/>
+      <c r="AM12" s="17"/>
     </row>
-    <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="24" t="s">
+    <row r="13" spans="1:39" ht="14.25" customHeight="1">
+      <c r="A13" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="25">
-        <v>1.0</v>
-      </c>
-      <c r="D13" s="26">
-        <v>45930.0</v>
-      </c>
-      <c r="E13" s="26">
-        <v>45935.0</v>
-      </c>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="24"/>
-      <c r="I13" s="24"/>
-      <c r="J13" s="24"/>
-      <c r="K13" s="24"/>
-      <c r="L13" s="24"/>
-      <c r="M13" s="24"/>
-      <c r="N13" s="24"/>
-      <c r="O13" s="24"/>
-      <c r="P13" s="24"/>
-      <c r="Q13" s="24"/>
-      <c r="R13" s="24"/>
-      <c r="S13" s="24"/>
-      <c r="T13" s="24"/>
-      <c r="U13" s="24"/>
-      <c r="V13" s="24"/>
-      <c r="W13" s="24"/>
-      <c r="X13" s="24"/>
-      <c r="Y13" s="24"/>
-      <c r="Z13" s="24"/>
-      <c r="AA13" s="24"/>
-      <c r="AB13" s="24"/>
-      <c r="AC13" s="24"/>
-      <c r="AD13" s="24"/>
-      <c r="AE13" s="24"/>
-      <c r="AF13" s="24"/>
-      <c r="AG13" s="24"/>
-      <c r="AH13" s="24"/>
-      <c r="AI13" s="24"/>
-      <c r="AJ13" s="24"/>
-      <c r="AK13" s="24"/>
-      <c r="AL13" s="24"/>
-      <c r="AM13" s="24"/>
+      <c r="C13" s="18">
+        <v>1</v>
+      </c>
+      <c r="D13" s="19">
+        <v>45930</v>
+      </c>
+      <c r="E13" s="19">
+        <v>45935</v>
+      </c>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17"/>
+      <c r="R13" s="17"/>
+      <c r="S13" s="17"/>
+      <c r="T13" s="17"/>
+      <c r="U13" s="17"/>
+      <c r="V13" s="17"/>
+      <c r="W13" s="17"/>
+      <c r="X13" s="17"/>
+      <c r="Y13" s="17"/>
+      <c r="Z13" s="17"/>
+      <c r="AA13" s="17"/>
+      <c r="AB13" s="17"/>
+      <c r="AC13" s="17"/>
+      <c r="AD13" s="17"/>
+      <c r="AE13" s="17"/>
+      <c r="AF13" s="17"/>
+      <c r="AG13" s="17"/>
+      <c r="AH13" s="17"/>
+      <c r="AI13" s="17"/>
+      <c r="AJ13" s="17"/>
+      <c r="AK13" s="17"/>
+      <c r="AL13" s="17"/>
+      <c r="AM13" s="17"/>
     </row>
-    <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="24" t="s">
+    <row r="14" spans="1:39" ht="14.25" customHeight="1">
+      <c r="A14" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="25">
-        <v>1.0</v>
-      </c>
-      <c r="D14" s="26">
-        <v>45930.0</v>
-      </c>
-      <c r="E14" s="26">
-        <v>45947.0</v>
-      </c>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="24"/>
-      <c r="K14" s="24"/>
-      <c r="L14" s="24"/>
-      <c r="M14" s="24"/>
-      <c r="N14" s="24"/>
-      <c r="O14" s="24"/>
-      <c r="P14" s="24"/>
-      <c r="Q14" s="24"/>
-      <c r="R14" s="24"/>
-      <c r="S14" s="24"/>
-      <c r="T14" s="24"/>
-      <c r="U14" s="24"/>
-      <c r="V14" s="24"/>
-      <c r="W14" s="24"/>
-      <c r="X14" s="24"/>
-      <c r="Y14" s="24"/>
-      <c r="Z14" s="24"/>
-      <c r="AA14" s="24"/>
-      <c r="AB14" s="24"/>
-      <c r="AC14" s="24"/>
-      <c r="AD14" s="24"/>
-      <c r="AE14" s="24"/>
-      <c r="AF14" s="24"/>
-      <c r="AG14" s="24"/>
-      <c r="AH14" s="24"/>
-      <c r="AI14" s="24"/>
-      <c r="AJ14" s="24"/>
-      <c r="AK14" s="24"/>
-      <c r="AL14" s="24"/>
-      <c r="AM14" s="24"/>
+      <c r="C14" s="18">
+        <v>1</v>
+      </c>
+      <c r="D14" s="19">
+        <v>45930</v>
+      </c>
+      <c r="E14" s="19">
+        <v>45947</v>
+      </c>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="17"/>
+      <c r="R14" s="17"/>
+      <c r="S14" s="17"/>
+      <c r="T14" s="17"/>
+      <c r="U14" s="17"/>
+      <c r="V14" s="17"/>
+      <c r="W14" s="17"/>
+      <c r="X14" s="17"/>
+      <c r="Y14" s="17"/>
+      <c r="Z14" s="17"/>
+      <c r="AA14" s="17"/>
+      <c r="AB14" s="17"/>
+      <c r="AC14" s="17"/>
+      <c r="AD14" s="17"/>
+      <c r="AE14" s="17"/>
+      <c r="AF14" s="17"/>
+      <c r="AG14" s="17"/>
+      <c r="AH14" s="17"/>
+      <c r="AI14" s="17"/>
+      <c r="AJ14" s="17"/>
+      <c r="AK14" s="17"/>
+      <c r="AL14" s="17"/>
+      <c r="AM14" s="17"/>
     </row>
-    <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="24" t="s">
+    <row r="15" spans="1:39" ht="14.25" customHeight="1">
+      <c r="A15" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="25">
-        <v>1.0</v>
-      </c>
-      <c r="D15" s="26">
-        <v>45930.0</v>
-      </c>
-      <c r="E15" s="26">
-        <v>45946.0</v>
-      </c>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="24"/>
-      <c r="K15" s="24"/>
-      <c r="L15" s="24"/>
-      <c r="M15" s="24"/>
-      <c r="N15" s="24"/>
-      <c r="O15" s="24"/>
-      <c r="P15" s="24"/>
-      <c r="Q15" s="24"/>
-      <c r="R15" s="24"/>
-      <c r="S15" s="24"/>
-      <c r="T15" s="24"/>
-      <c r="U15" s="24"/>
-      <c r="V15" s="24"/>
-      <c r="W15" s="24"/>
-      <c r="X15" s="24"/>
-      <c r="Y15" s="24"/>
-      <c r="Z15" s="24"/>
-      <c r="AA15" s="24"/>
-      <c r="AB15" s="24"/>
-      <c r="AC15" s="24"/>
-      <c r="AD15" s="24"/>
-      <c r="AE15" s="24"/>
-      <c r="AF15" s="24"/>
-      <c r="AG15" s="24"/>
-      <c r="AH15" s="24"/>
-      <c r="AI15" s="24"/>
-      <c r="AJ15" s="24"/>
-      <c r="AK15" s="24"/>
-      <c r="AL15" s="24"/>
-      <c r="AM15" s="24"/>
+      <c r="C15" s="18">
+        <v>1</v>
+      </c>
+      <c r="D15" s="19">
+        <v>45930</v>
+      </c>
+      <c r="E15" s="19">
+        <v>45946</v>
+      </c>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="R15" s="17"/>
+      <c r="S15" s="17"/>
+      <c r="T15" s="17"/>
+      <c r="U15" s="17"/>
+      <c r="V15" s="17"/>
+      <c r="W15" s="17"/>
+      <c r="X15" s="17"/>
+      <c r="Y15" s="17"/>
+      <c r="Z15" s="17"/>
+      <c r="AA15" s="17"/>
+      <c r="AB15" s="17"/>
+      <c r="AC15" s="17"/>
+      <c r="AD15" s="17"/>
+      <c r="AE15" s="17"/>
+      <c r="AF15" s="17"/>
+      <c r="AG15" s="17"/>
+      <c r="AH15" s="17"/>
+      <c r="AI15" s="17"/>
+      <c r="AJ15" s="17"/>
+      <c r="AK15" s="17"/>
+      <c r="AL15" s="17"/>
+      <c r="AM15" s="17"/>
     </row>
-    <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="24" t="s">
+    <row r="16" spans="1:39" ht="14.25" customHeight="1">
+      <c r="A16" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="25">
-        <v>1.0</v>
-      </c>
-      <c r="D16" s="26">
-        <v>45930.0</v>
-      </c>
-      <c r="E16" s="26">
-        <v>45945.0</v>
-      </c>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="24"/>
-      <c r="K16" s="24"/>
-      <c r="L16" s="24"/>
-      <c r="M16" s="24"/>
-      <c r="N16" s="24"/>
-      <c r="O16" s="24"/>
-      <c r="P16" s="24"/>
-      <c r="Q16" s="24"/>
-      <c r="R16" s="24"/>
-      <c r="S16" s="24"/>
-      <c r="T16" s="24"/>
-      <c r="U16" s="24"/>
-      <c r="V16" s="24"/>
-      <c r="W16" s="24"/>
-      <c r="X16" s="24"/>
-      <c r="Y16" s="24"/>
-      <c r="Z16" s="24"/>
-      <c r="AA16" s="24"/>
-      <c r="AB16" s="24"/>
-      <c r="AC16" s="24"/>
-      <c r="AD16" s="24"/>
-      <c r="AE16" s="24"/>
-      <c r="AF16" s="24"/>
-      <c r="AG16" s="24"/>
-      <c r="AH16" s="24"/>
-      <c r="AI16" s="24"/>
-      <c r="AJ16" s="24"/>
-      <c r="AK16" s="24"/>
-      <c r="AL16" s="24"/>
-      <c r="AM16" s="24"/>
+      <c r="C16" s="18">
+        <v>1</v>
+      </c>
+      <c r="D16" s="19">
+        <v>45930</v>
+      </c>
+      <c r="E16" s="19">
+        <v>45945</v>
+      </c>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="17"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="17"/>
+      <c r="R16" s="17"/>
+      <c r="S16" s="17"/>
+      <c r="T16" s="17"/>
+      <c r="U16" s="17"/>
+      <c r="V16" s="17"/>
+      <c r="W16" s="17"/>
+      <c r="X16" s="17"/>
+      <c r="Y16" s="17"/>
+      <c r="Z16" s="17"/>
+      <c r="AA16" s="17"/>
+      <c r="AB16" s="17"/>
+      <c r="AC16" s="17"/>
+      <c r="AD16" s="17"/>
+      <c r="AE16" s="17"/>
+      <c r="AF16" s="17"/>
+      <c r="AG16" s="17"/>
+      <c r="AH16" s="17"/>
+      <c r="AI16" s="17"/>
+      <c r="AJ16" s="17"/>
+      <c r="AK16" s="17"/>
+      <c r="AL16" s="17"/>
+      <c r="AM16" s="17"/>
     </row>
-    <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="24" t="s">
+    <row r="17" spans="1:39" ht="14.25" customHeight="1">
+      <c r="A17" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="25">
-        <v>1.0</v>
-      </c>
-      <c r="D17" s="26">
-        <v>45930.0</v>
-      </c>
-      <c r="E17" s="26">
-        <v>45947.0</v>
-      </c>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="24"/>
-      <c r="K17" s="24"/>
-      <c r="L17" s="24"/>
-      <c r="M17" s="24"/>
-      <c r="N17" s="24"/>
-      <c r="O17" s="24"/>
-      <c r="P17" s="24"/>
-      <c r="Q17" s="24"/>
-      <c r="R17" s="24"/>
-      <c r="S17" s="24"/>
-      <c r="T17" s="24"/>
-      <c r="U17" s="24"/>
-      <c r="V17" s="24"/>
-      <c r="W17" s="24"/>
-      <c r="X17" s="24"/>
-      <c r="Y17" s="24"/>
-      <c r="Z17" s="24"/>
-      <c r="AA17" s="24"/>
-      <c r="AB17" s="24"/>
-      <c r="AC17" s="24"/>
-      <c r="AD17" s="24"/>
-      <c r="AE17" s="24"/>
-      <c r="AF17" s="24"/>
-      <c r="AG17" s="24"/>
-      <c r="AH17" s="24"/>
-      <c r="AI17" s="24"/>
-      <c r="AJ17" s="24"/>
-      <c r="AK17" s="24"/>
-      <c r="AL17" s="24"/>
-      <c r="AM17" s="24"/>
+      <c r="C17" s="18">
+        <v>1</v>
+      </c>
+      <c r="D17" s="19">
+        <v>45930</v>
+      </c>
+      <c r="E17" s="19">
+        <v>45947</v>
+      </c>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="17"/>
+      <c r="R17" s="17"/>
+      <c r="S17" s="17"/>
+      <c r="T17" s="17"/>
+      <c r="U17" s="17"/>
+      <c r="V17" s="17"/>
+      <c r="W17" s="17"/>
+      <c r="X17" s="17"/>
+      <c r="Y17" s="17"/>
+      <c r="Z17" s="17"/>
+      <c r="AA17" s="17"/>
+      <c r="AB17" s="17"/>
+      <c r="AC17" s="17"/>
+      <c r="AD17" s="17"/>
+      <c r="AE17" s="17"/>
+      <c r="AF17" s="17"/>
+      <c r="AG17" s="17"/>
+      <c r="AH17" s="17"/>
+      <c r="AI17" s="17"/>
+      <c r="AJ17" s="17"/>
+      <c r="AK17" s="17"/>
+      <c r="AL17" s="17"/>
+      <c r="AM17" s="17"/>
     </row>
-    <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="23" t="s">
+    <row r="18" spans="1:39" ht="14.25" customHeight="1">
+      <c r="A18" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="24"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="24"/>
-      <c r="J18" s="24"/>
-      <c r="K18" s="24"/>
-      <c r="L18" s="24"/>
-      <c r="M18" s="24"/>
-      <c r="N18" s="24"/>
-      <c r="O18" s="24"/>
-      <c r="P18" s="24"/>
-      <c r="Q18" s="24"/>
-      <c r="R18" s="24"/>
-      <c r="S18" s="24"/>
-      <c r="T18" s="24"/>
-      <c r="U18" s="24"/>
-      <c r="V18" s="24"/>
-      <c r="W18" s="24"/>
-      <c r="X18" s="24"/>
-      <c r="Y18" s="24"/>
-      <c r="Z18" s="24"/>
-      <c r="AA18" s="24"/>
-      <c r="AB18" s="24"/>
-      <c r="AC18" s="24"/>
-      <c r="AD18" s="24"/>
-      <c r="AE18" s="24"/>
-      <c r="AF18" s="24"/>
-      <c r="AG18" s="24"/>
-      <c r="AH18" s="24"/>
-      <c r="AI18" s="24"/>
-      <c r="AJ18" s="24"/>
-      <c r="AK18" s="24"/>
-      <c r="AL18" s="24"/>
-      <c r="AM18" s="24"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="17"/>
+      <c r="M18" s="17"/>
+      <c r="N18" s="17"/>
+      <c r="O18" s="17"/>
+      <c r="P18" s="17"/>
+      <c r="Q18" s="17"/>
+      <c r="R18" s="17"/>
+      <c r="S18" s="17"/>
+      <c r="T18" s="17"/>
+      <c r="U18" s="17"/>
+      <c r="V18" s="17"/>
+      <c r="W18" s="17"/>
+      <c r="X18" s="17"/>
+      <c r="Y18" s="17"/>
+      <c r="Z18" s="17"/>
+      <c r="AA18" s="17"/>
+      <c r="AB18" s="17"/>
+      <c r="AC18" s="17"/>
+      <c r="AD18" s="17"/>
+      <c r="AE18" s="17"/>
+      <c r="AF18" s="17"/>
+      <c r="AG18" s="17"/>
+      <c r="AH18" s="17"/>
+      <c r="AI18" s="17"/>
+      <c r="AJ18" s="17"/>
+      <c r="AK18" s="17"/>
+      <c r="AL18" s="17"/>
+      <c r="AM18" s="17"/>
     </row>
-    <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="24" t="s">
+    <row r="19" spans="1:39" ht="14.25" customHeight="1">
+      <c r="A19" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="24" t="s">
+      <c r="B19" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="25">
-        <v>1.0</v>
-      </c>
-      <c r="D19" s="26">
-        <v>45930.0</v>
-      </c>
-      <c r="E19" s="26">
-        <v>45947.0</v>
-      </c>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="24"/>
-      <c r="I19" s="24"/>
-      <c r="J19" s="24"/>
-      <c r="K19" s="24"/>
-      <c r="L19" s="24"/>
-      <c r="M19" s="24"/>
-      <c r="N19" s="24"/>
-      <c r="O19" s="24"/>
-      <c r="P19" s="24"/>
-      <c r="Q19" s="24"/>
-      <c r="R19" s="24"/>
-      <c r="S19" s="24"/>
-      <c r="T19" s="24"/>
-      <c r="U19" s="24"/>
-      <c r="V19" s="24"/>
-      <c r="W19" s="24"/>
-      <c r="X19" s="24"/>
-      <c r="Y19" s="24"/>
-      <c r="Z19" s="24"/>
-      <c r="AA19" s="24"/>
-      <c r="AB19" s="24"/>
-      <c r="AC19" s="24"/>
-      <c r="AD19" s="24"/>
-      <c r="AE19" s="24"/>
-      <c r="AF19" s="24"/>
-      <c r="AG19" s="24"/>
-      <c r="AH19" s="24"/>
-      <c r="AI19" s="24"/>
-      <c r="AJ19" s="24"/>
-      <c r="AK19" s="24"/>
-      <c r="AL19" s="24"/>
-      <c r="AM19" s="24"/>
+      <c r="C19" s="18">
+        <v>1</v>
+      </c>
+      <c r="D19" s="19">
+        <v>45930</v>
+      </c>
+      <c r="E19" s="19">
+        <v>45947</v>
+      </c>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="17"/>
+      <c r="M19" s="17"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="17"/>
+      <c r="Q19" s="17"/>
+      <c r="R19" s="17"/>
+      <c r="S19" s="17"/>
+      <c r="T19" s="17"/>
+      <c r="U19" s="17"/>
+      <c r="V19" s="17"/>
+      <c r="W19" s="17"/>
+      <c r="X19" s="17"/>
+      <c r="Y19" s="17"/>
+      <c r="Z19" s="17"/>
+      <c r="AA19" s="17"/>
+      <c r="AB19" s="17"/>
+      <c r="AC19" s="17"/>
+      <c r="AD19" s="17"/>
+      <c r="AE19" s="17"/>
+      <c r="AF19" s="17"/>
+      <c r="AG19" s="17"/>
+      <c r="AH19" s="17"/>
+      <c r="AI19" s="17"/>
+      <c r="AJ19" s="17"/>
+      <c r="AK19" s="17"/>
+      <c r="AL19" s="17"/>
+      <c r="AM19" s="17"/>
     </row>
-    <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="24" t="s">
+    <row r="20" spans="1:39" ht="14.25" customHeight="1">
+      <c r="A20" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="24" t="s">
+      <c r="B20" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="25">
-        <v>1.0</v>
-      </c>
-      <c r="D20" s="26">
-        <v>45930.0</v>
-      </c>
-      <c r="E20" s="26">
-        <v>45939.0</v>
-      </c>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="24"/>
-      <c r="I20" s="24"/>
-      <c r="J20" s="24"/>
-      <c r="K20" s="24"/>
-      <c r="L20" s="24"/>
-      <c r="M20" s="24"/>
-      <c r="N20" s="24"/>
-      <c r="O20" s="24"/>
-      <c r="P20" s="24"/>
-      <c r="Q20" s="24"/>
-      <c r="R20" s="24"/>
-      <c r="S20" s="24"/>
-      <c r="T20" s="24"/>
-      <c r="U20" s="24"/>
-      <c r="V20" s="24"/>
-      <c r="W20" s="24"/>
-      <c r="X20" s="24"/>
-      <c r="Y20" s="24"/>
-      <c r="Z20" s="24"/>
-      <c r="AA20" s="24"/>
-      <c r="AB20" s="24"/>
-      <c r="AC20" s="24"/>
-      <c r="AD20" s="24"/>
-      <c r="AE20" s="24"/>
-      <c r="AF20" s="24"/>
-      <c r="AG20" s="24"/>
-      <c r="AH20" s="24"/>
-      <c r="AI20" s="24"/>
-      <c r="AJ20" s="24"/>
-      <c r="AK20" s="24"/>
-      <c r="AL20" s="24"/>
-      <c r="AM20" s="24"/>
+      <c r="C20" s="18">
+        <v>1</v>
+      </c>
+      <c r="D20" s="19">
+        <v>45930</v>
+      </c>
+      <c r="E20" s="19">
+        <v>45939</v>
+      </c>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="17"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="17"/>
+      <c r="R20" s="17"/>
+      <c r="S20" s="17"/>
+      <c r="T20" s="17"/>
+      <c r="U20" s="17"/>
+      <c r="V20" s="17"/>
+      <c r="W20" s="17"/>
+      <c r="X20" s="17"/>
+      <c r="Y20" s="17"/>
+      <c r="Z20" s="17"/>
+      <c r="AA20" s="17"/>
+      <c r="AB20" s="17"/>
+      <c r="AC20" s="17"/>
+      <c r="AD20" s="17"/>
+      <c r="AE20" s="17"/>
+      <c r="AF20" s="17"/>
+      <c r="AG20" s="17"/>
+      <c r="AH20" s="17"/>
+      <c r="AI20" s="17"/>
+      <c r="AJ20" s="17"/>
+      <c r="AK20" s="17"/>
+      <c r="AL20" s="17"/>
+      <c r="AM20" s="17"/>
     </row>
-    <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="24" t="s">
+    <row r="21" spans="1:39" ht="14.25" customHeight="1">
+      <c r="A21" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="25">
-        <v>1.0</v>
-      </c>
-      <c r="D21" s="26">
-        <v>45930.0</v>
-      </c>
-      <c r="E21" s="26">
-        <v>45935.0</v>
-      </c>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="24"/>
-      <c r="K21" s="24"/>
-      <c r="L21" s="24"/>
-      <c r="M21" s="24"/>
-      <c r="N21" s="24"/>
-      <c r="O21" s="24"/>
-      <c r="P21" s="24"/>
-      <c r="Q21" s="24"/>
-      <c r="R21" s="24"/>
-      <c r="S21" s="24"/>
-      <c r="T21" s="24"/>
-      <c r="U21" s="24"/>
-      <c r="V21" s="24"/>
-      <c r="W21" s="24"/>
-      <c r="X21" s="24"/>
-      <c r="Y21" s="24"/>
-      <c r="Z21" s="24"/>
-      <c r="AA21" s="24"/>
-      <c r="AB21" s="24"/>
-      <c r="AC21" s="24"/>
-      <c r="AD21" s="24"/>
-      <c r="AE21" s="24"/>
-      <c r="AF21" s="24"/>
-      <c r="AG21" s="24"/>
-      <c r="AH21" s="24"/>
-      <c r="AI21" s="24"/>
-      <c r="AJ21" s="24"/>
-      <c r="AK21" s="24"/>
-      <c r="AL21" s="24"/>
-      <c r="AM21" s="24"/>
+      <c r="C21" s="18">
+        <v>1</v>
+      </c>
+      <c r="D21" s="19">
+        <v>45930</v>
+      </c>
+      <c r="E21" s="19">
+        <v>45935</v>
+      </c>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="17"/>
+      <c r="L21" s="17"/>
+      <c r="M21" s="17"/>
+      <c r="N21" s="17"/>
+      <c r="O21" s="17"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="17"/>
+      <c r="R21" s="17"/>
+      <c r="S21" s="17"/>
+      <c r="T21" s="17"/>
+      <c r="U21" s="17"/>
+      <c r="V21" s="17"/>
+      <c r="W21" s="17"/>
+      <c r="X21" s="17"/>
+      <c r="Y21" s="17"/>
+      <c r="Z21" s="17"/>
+      <c r="AA21" s="17"/>
+      <c r="AB21" s="17"/>
+      <c r="AC21" s="17"/>
+      <c r="AD21" s="17"/>
+      <c r="AE21" s="17"/>
+      <c r="AF21" s="17"/>
+      <c r="AG21" s="17"/>
+      <c r="AH21" s="17"/>
+      <c r="AI21" s="17"/>
+      <c r="AJ21" s="17"/>
+      <c r="AK21" s="17"/>
+      <c r="AL21" s="17"/>
+      <c r="AM21" s="17"/>
     </row>
-    <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="24" t="s">
+    <row r="22" spans="1:39" ht="14.25" customHeight="1">
+      <c r="A22" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C22" s="25">
-        <v>1.0</v>
-      </c>
-      <c r="D22" s="26">
-        <v>45930.0</v>
-      </c>
-      <c r="E22" s="26">
-        <v>45934.0</v>
-      </c>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="24"/>
-      <c r="I22" s="24"/>
-      <c r="J22" s="24"/>
-      <c r="K22" s="24"/>
-      <c r="L22" s="24"/>
-      <c r="M22" s="24"/>
-      <c r="N22" s="24"/>
-      <c r="O22" s="24"/>
-      <c r="P22" s="24"/>
-      <c r="Q22" s="24"/>
-      <c r="R22" s="24"/>
-      <c r="S22" s="24"/>
-      <c r="T22" s="24"/>
-      <c r="U22" s="24"/>
-      <c r="V22" s="24"/>
-      <c r="W22" s="24"/>
-      <c r="X22" s="24"/>
-      <c r="Y22" s="24"/>
-      <c r="Z22" s="24"/>
-      <c r="AA22" s="24"/>
-      <c r="AB22" s="24"/>
-      <c r="AC22" s="24"/>
-      <c r="AD22" s="24"/>
-      <c r="AE22" s="24"/>
-      <c r="AF22" s="24"/>
-      <c r="AG22" s="24"/>
-      <c r="AH22" s="24"/>
-      <c r="AI22" s="24"/>
-      <c r="AJ22" s="24"/>
-      <c r="AK22" s="24"/>
-      <c r="AL22" s="24"/>
-      <c r="AM22" s="24"/>
+      <c r="C22" s="18">
+        <v>1</v>
+      </c>
+      <c r="D22" s="19">
+        <v>45930</v>
+      </c>
+      <c r="E22" s="19">
+        <v>45934</v>
+      </c>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="17"/>
+      <c r="L22" s="17"/>
+      <c r="M22" s="17"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="17"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="17"/>
+      <c r="R22" s="17"/>
+      <c r="S22" s="17"/>
+      <c r="T22" s="17"/>
+      <c r="U22" s="17"/>
+      <c r="V22" s="17"/>
+      <c r="W22" s="17"/>
+      <c r="X22" s="17"/>
+      <c r="Y22" s="17"/>
+      <c r="Z22" s="17"/>
+      <c r="AA22" s="17"/>
+      <c r="AB22" s="17"/>
+      <c r="AC22" s="17"/>
+      <c r="AD22" s="17"/>
+      <c r="AE22" s="17"/>
+      <c r="AF22" s="17"/>
+      <c r="AG22" s="17"/>
+      <c r="AH22" s="17"/>
+      <c r="AI22" s="17"/>
+      <c r="AJ22" s="17"/>
+      <c r="AK22" s="17"/>
+      <c r="AL22" s="17"/>
+      <c r="AM22" s="17"/>
     </row>
-    <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="30"/>
-      <c r="B23" s="30"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="30"/>
-      <c r="I23" s="30"/>
-      <c r="J23" s="30"/>
-      <c r="K23" s="30"/>
-      <c r="L23" s="30"/>
-      <c r="M23" s="30"/>
-      <c r="N23" s="30"/>
-      <c r="O23" s="30"/>
-      <c r="P23" s="30"/>
-      <c r="Q23" s="30"/>
-      <c r="R23" s="30"/>
-      <c r="S23" s="30"/>
-      <c r="T23" s="30"/>
-      <c r="U23" s="30"/>
-      <c r="V23" s="30"/>
-      <c r="W23" s="30"/>
-      <c r="X23" s="30"/>
-      <c r="Y23" s="30"/>
-      <c r="Z23" s="30"/>
-      <c r="AA23" s="30"/>
-      <c r="AB23" s="30"/>
-      <c r="AC23" s="30"/>
-      <c r="AD23" s="30"/>
-      <c r="AE23" s="30"/>
-      <c r="AF23" s="30"/>
-      <c r="AG23" s="30"/>
-      <c r="AH23" s="30"/>
-      <c r="AI23" s="30"/>
-      <c r="AJ23" s="30"/>
-      <c r="AK23" s="30"/>
-      <c r="AL23" s="30"/>
-      <c r="AM23" s="30"/>
+    <row r="23" spans="1:39" ht="14.25" customHeight="1">
+      <c r="A23" s="23"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="23"/>
+      <c r="K23" s="23"/>
+      <c r="L23" s="23"/>
+      <c r="M23" s="23"/>
+      <c r="N23" s="23"/>
+      <c r="O23" s="23"/>
+      <c r="P23" s="23"/>
+      <c r="Q23" s="23"/>
+      <c r="R23" s="23"/>
+      <c r="S23" s="23"/>
+      <c r="T23" s="23"/>
+      <c r="U23" s="23"/>
+      <c r="V23" s="23"/>
+      <c r="W23" s="23"/>
+      <c r="X23" s="23"/>
+      <c r="Y23" s="23"/>
+      <c r="Z23" s="23"/>
+      <c r="AA23" s="23"/>
+      <c r="AB23" s="23"/>
+      <c r="AC23" s="23"/>
+      <c r="AD23" s="23"/>
+      <c r="AE23" s="23"/>
+      <c r="AF23" s="23"/>
+      <c r="AG23" s="23"/>
+      <c r="AH23" s="23"/>
+      <c r="AI23" s="23"/>
+      <c r="AJ23" s="23"/>
+      <c r="AK23" s="23"/>
+      <c r="AL23" s="23"/>
+      <c r="AM23" s="23"/>
     </row>
-    <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="33"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="35"/>
+    <row r="24" spans="1:39" ht="14.25" customHeight="1">
+      <c r="A24" s="26"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="28"/>
     </row>
-    <row r="25" ht="14.25" customHeight="1">
-      <c r="D25" s="35"/>
-      <c r="E25" s="35"/>
+    <row r="25" spans="1:39" ht="14.25" customHeight="1">
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
     </row>
-    <row r="26" ht="14.25" customHeight="1"/>
-    <row r="27" ht="14.25" customHeight="1"/>
-    <row r="28" ht="14.25" customHeight="1"/>
-    <row r="29" ht="14.25" customHeight="1"/>
-    <row r="30" ht="14.25" customHeight="1"/>
-    <row r="31" ht="14.25" customHeight="1"/>
-    <row r="32" ht="14.25" customHeight="1">
-      <c r="D32" s="36"/>
+    <row r="26" spans="1:39" ht="14.25" customHeight="1"/>
+    <row r="27" spans="1:39" ht="14.25" customHeight="1"/>
+    <row r="28" spans="1:39" ht="14.25" customHeight="1"/>
+    <row r="29" spans="1:39" ht="14.25" customHeight="1"/>
+    <row r="30" spans="1:39" ht="14.25" customHeight="1"/>
+    <row r="31" spans="1:39" ht="14.25" customHeight="1"/>
+    <row r="32" spans="1:39" ht="14.25" customHeight="1">
+      <c r="D32" s="29"/>
     </row>
     <row r="33" ht="14.25" customHeight="1"/>
     <row r="34" ht="14.25" customHeight="1"/>
@@ -5133,26 +5203,22 @@
     <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="D5:E5"/>
     <mergeCell ref="G4:K4"/>
     <mergeCell ref="L4:R4"/>
     <mergeCell ref="S4:Y4"/>
     <mergeCell ref="Z4:AF4"/>
     <mergeCell ref="AG4:AM4"/>
-    <mergeCell ref="D5:E5"/>
   </mergeCells>
   <conditionalFormatting sqref="G7:AM23">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>AND(G$5&gt;=$D7,G$5&lt;=((($E7-$D7+1)*$C7)+$D7-1))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G7:AM23">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>AND(G$5&gt;=$D7,G$5&lt;=$E7)</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>